--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\Batches\22club2_LJ_4PM\DS\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{845DFB44-C738-41C6-8835-0638C6528BFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8547A16D-F221-4066-BF83-6E283BBA590D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="378" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="19">
   <si>
     <t>Name</t>
   </si>
@@ -531,7 +531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AC14"/>
+  <dimension ref="A1:AE14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -543,10 +543,10 @@
     <col min="17" max="18" width="5.33203125" bestFit="1" customWidth="1"/>
     <col min="19" max="25" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="31" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -634,8 +634,14 @@
       <c r="AC1" s="1">
         <v>45553</v>
       </c>
+      <c r="AD1" s="1">
+        <v>45583</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>45588</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -723,8 +729,14 @@
       <c r="AC2" t="s">
         <v>10</v>
       </c>
+      <c r="AD2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -812,8 +824,14 @@
       <c r="AC3" t="s">
         <v>11</v>
       </c>
+      <c r="AD3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -901,8 +919,14 @@
       <c r="AC4" t="s">
         <v>10</v>
       </c>
+      <c r="AD4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -990,8 +1014,14 @@
       <c r="AC5" t="s">
         <v>10</v>
       </c>
+      <c r="AD5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1079,8 +1109,14 @@
       <c r="AC6" t="s">
         <v>9</v>
       </c>
+      <c r="AD6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1168,8 +1204,14 @@
       <c r="AC7" t="s">
         <v>10</v>
       </c>
+      <c r="AD7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1257,8 +1299,14 @@
       <c r="AC8" t="s">
         <v>10</v>
       </c>
+      <c r="AD8" t="s">
+        <v>11</v>
+      </c>
+      <c r="AE8" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1346,8 +1394,14 @@
       <c r="AC9" t="s">
         <v>10</v>
       </c>
+      <c r="AD9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE9" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1435,8 +1489,14 @@
       <c r="AC10" t="s">
         <v>10</v>
       </c>
+      <c r="AD10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AE10" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1524,8 +1584,14 @@
       <c r="AC11" t="s">
         <v>10</v>
       </c>
+      <c r="AD11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1613,8 +1679,14 @@
       <c r="AC12" t="s">
         <v>10</v>
       </c>
+      <c r="AD12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1702,8 +1774,14 @@
       <c r="AC13" t="s">
         <v>17</v>
       </c>
+      <c r="AD13" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE13" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1789,6 +1867,12 @@
         <v>17</v>
       </c>
       <c r="AC14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AD14" t="s">
+        <v>17</v>
+      </c>
+      <c r="AE14" t="s">
         <v>17</v>
       </c>
     </row>

--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -8,12 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8547A16D-F221-4066-BF83-6E283BBA590D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98C6570-F9B3-4151-ADE7-2470FA86FDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -25,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -78,10 +80,19 @@
     <t>Dhruvi Desai</t>
   </si>
   <si>
-    <t>-</t>
+    <t>Bhavya Patel</t>
   </si>
   <si>
-    <t>Bhavya Patel</t>
+    <t>Attendance Points/5</t>
+  </si>
+  <si>
+    <t>Total Attendance Points/155</t>
+  </si>
+  <si>
+    <t>Test Marks</t>
+  </si>
+  <si>
+    <t>Test Performance/5</t>
   </si>
 </sst>
 </file>
@@ -207,6 +218,76 @@
 </xdr:wsDr>
 </file>
 
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>190500</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>150120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>27</xdr:col>
+      <xdr:colOff>191940</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>175680</xdr:rowOff>
+    </xdr:to>
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+          <xdr14:nvContentPartPr>
+            <xdr14:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{53BE9AF2-C863-43B7-867A-4337F8A65104}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr14:cNvPr>
+            <xdr14:cNvContentPartPr/>
+          </xdr14:nvContentPartPr>
+          <xdr14:nvPr macro=""/>
+          <xdr14:xfrm>
+            <a:off x="13304520" y="150120"/>
+            <a:ext cx="1440" cy="25560"/>
+          </xdr14:xfrm>
+        </xdr:contentPart>
+      </mc:Choice>
+      <mc:Fallback xmlns="">
+        <xdr:pic>
+          <xdr:nvPicPr>
+            <xdr:cNvPr id="2" name="Ink 1">
+              <a:extLst>
+                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8213C462-8350-4C50-1FF1-0132C3A2AF48}"/>
+                </a:ext>
+              </a:extLst>
+            </xdr:cNvPr>
+            <xdr:cNvPicPr/>
+          </xdr:nvPicPr>
+          <xdr:blipFill>
+            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+            <a:stretch>
+              <a:fillRect/>
+            </a:stretch>
+          </xdr:blipFill>
+          <xdr:spPr>
+            <a:xfrm>
+              <a:off x="13298400" y="144000"/>
+              <a:ext cx="13680" cy="37800"/>
+            </a:xfrm>
+            <a:prstGeom prst="rect">
+              <a:avLst/>
+            </a:prstGeom>
+          </xdr:spPr>
+        </xdr:pic>
+      </mc:Fallback>
+    </mc:AlternateContent>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/ink/ink1.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
@@ -224,6 +305,33 @@
         </inkml:channelProperties>
       </inkml:inkSource>
       <inkml:timestamp xml:id="ts0" timeString="2024-08-30T12:01:52.725"/>
+    </inkml:context>
+    <inkml:brush xml:id="br0">
+      <inkml:brushProperty name="width" value="0.035" units="cm"/>
+      <inkml:brushProperty name="height" value="0.035" units="cm"/>
+    </inkml:brush>
+  </inkml:definitions>
+  <inkml:trace contextRef="#ctx0" brushRef="#br0">4 70 7555,'0'-15'4194,"0"1"-3281,0 0 239,-3 4 49,3 5 159,0 3-623,3-1-97,-3 1-144,0 0-127,-3-1-321</inkml:trace>
+</inkml:ink>
+</file>
+
+<file path=xl/ink/ink2.xml><?xml version="1.0" encoding="utf-8"?>
+<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
+  <inkml:definitions>
+    <inkml:context xml:id="ctx0">
+      <inkml:inkSource xml:id="inkSrc0">
+        <inkml:traceFormat>
+          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
+          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
+        </inkml:traceFormat>
+        <inkml:channelProperties>
+          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
+          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
+        </inkml:channelProperties>
+      </inkml:inkSource>
+      <inkml:timestamp xml:id="ts0" timeString="2024-10-26T02:28:14.003"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
       <inkml:brushProperty name="width" value="0.035" units="cm"/>
@@ -531,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AE14"/>
+  <dimension ref="A1:AF14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -546,7 +654,7 @@
     <col min="28" max="31" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -640,8 +748,11 @@
       <c r="AE1" s="1">
         <v>45588</v>
       </c>
+      <c r="AF1" s="1">
+        <v>45590</v>
+      </c>
     </row>
-    <row r="2" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -735,10 +846,13 @@
       <c r="AE2" t="s">
         <v>10</v>
       </c>
+      <c r="AF2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
         <v>13</v>
@@ -830,8 +944,11 @@
       <c r="AE3" t="s">
         <v>10</v>
       </c>
+      <c r="AF3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -925,8 +1042,11 @@
       <c r="AE4" t="s">
         <v>9</v>
       </c>
+      <c r="AF4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1020,8 +1140,11 @@
       <c r="AE5" t="s">
         <v>9</v>
       </c>
+      <c r="AF5" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1115,8 +1238,11 @@
       <c r="AE6" t="s">
         <v>9</v>
       </c>
+      <c r="AF6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1210,8 +1336,11 @@
       <c r="AE7" t="s">
         <v>10</v>
       </c>
+      <c r="AF7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1305,8 +1434,11 @@
       <c r="AE8" t="s">
         <v>11</v>
       </c>
+      <c r="AF8" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1400,8 +1532,11 @@
       <c r="AE9" t="s">
         <v>9</v>
       </c>
+      <c r="AF9" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1495,8 +1630,11 @@
       <c r="AE10" t="s">
         <v>9</v>
       </c>
+      <c r="AF10" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1590,8 +1728,11 @@
       <c r="AE11" t="s">
         <v>10</v>
       </c>
+      <c r="AF11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1685,8 +1826,11 @@
       <c r="AE12" t="s">
         <v>10</v>
       </c>
+      <c r="AF12" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1763,25 +1907,28 @@
         <v>9</v>
       </c>
       <c r="Z13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AB13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AC13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AD13" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE13" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="AF13" t="s">
+        <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:31" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -1858,22 +2005,25 @@
         <v>10</v>
       </c>
       <c r="Z14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AA14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AB14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AC14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AD14" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AE14" t="s">
-        <v>17</v>
+        <v>13</v>
+      </c>
+      <c r="AF14" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1883,4 +2033,2097 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA73659-E93B-42DB-A97C-57B09528EE56}">
+  <dimension ref="A1:AF14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="4" width="7" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="6.21875" bestFit="1" customWidth="1"/>
+    <col min="13" max="16" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="19" max="25" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
+    <col min="28" max="32" width="6.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
+        <v>45374</v>
+      </c>
+      <c r="C1" s="1">
+        <v>45381</v>
+      </c>
+      <c r="D1" s="1">
+        <v>45382</v>
+      </c>
+      <c r="E1" s="1">
+        <v>45387</v>
+      </c>
+      <c r="F1" s="1">
+        <v>45388</v>
+      </c>
+      <c r="G1" s="1">
+        <v>45394</v>
+      </c>
+      <c r="H1" s="1">
+        <v>45395</v>
+      </c>
+      <c r="I1" s="1">
+        <v>45401</v>
+      </c>
+      <c r="J1" s="1">
+        <v>45402</v>
+      </c>
+      <c r="K1" s="1">
+        <v>45415</v>
+      </c>
+      <c r="L1" s="1">
+        <v>45420</v>
+      </c>
+      <c r="M1" s="1">
+        <v>45422</v>
+      </c>
+      <c r="N1" s="1">
+        <v>45423</v>
+      </c>
+      <c r="O1" s="1">
+        <v>45441</v>
+      </c>
+      <c r="P1" s="1">
+        <v>45443</v>
+      </c>
+      <c r="Q1" s="1">
+        <v>45444</v>
+      </c>
+      <c r="R1" s="1">
+        <v>45448</v>
+      </c>
+      <c r="S1" s="1">
+        <v>45455</v>
+      </c>
+      <c r="T1" s="1">
+        <v>45457</v>
+      </c>
+      <c r="U1" s="1">
+        <v>45458</v>
+      </c>
+      <c r="V1" s="1">
+        <v>45462</v>
+      </c>
+      <c r="W1" s="1">
+        <v>45464</v>
+      </c>
+      <c r="X1" s="1">
+        <v>45465</v>
+      </c>
+      <c r="Y1" s="1">
+        <v>45472</v>
+      </c>
+      <c r="Z1" s="1">
+        <v>45532</v>
+      </c>
+      <c r="AA1" s="1">
+        <v>45534</v>
+      </c>
+      <c r="AB1" s="1">
+        <v>45546</v>
+      </c>
+      <c r="AC1" s="1">
+        <v>45553</v>
+      </c>
+      <c r="AD1" s="1">
+        <v>45583</v>
+      </c>
+      <c r="AE1" s="1">
+        <v>45588</v>
+      </c>
+      <c r="AF1" s="1">
+        <v>45590</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <f>_xlfn.IFS(Attendance!B2="P", 5, Attendance!B2="O",3,Attendance!B2="A",0, Attendance!B2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C2">
+        <f>_xlfn.IFS(Attendance!C2="P", 5, Attendance!C2="O",3,Attendance!C2="A",0, Attendance!C2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <f>_xlfn.IFS(Attendance!D2="P", 5, Attendance!D2="O",3,Attendance!D2="A",0, Attendance!D2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E2">
+        <f>_xlfn.IFS(Attendance!E2="P", 5, Attendance!E2="O",3,Attendance!E2="A",0, Attendance!E2="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="F2">
+        <f>_xlfn.IFS(Attendance!F2="P", 5, Attendance!F2="O",3,Attendance!F2="A",0, Attendance!F2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G2">
+        <f>_xlfn.IFS(Attendance!G2="P", 5, Attendance!G2="O",3,Attendance!G2="A",0, Attendance!G2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H2">
+        <f>_xlfn.IFS(Attendance!H2="P", 5, Attendance!H2="O",3,Attendance!H2="A",0, Attendance!H2="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="I2">
+        <f>_xlfn.IFS(Attendance!I2="P", 5, Attendance!I2="O",3,Attendance!I2="A",0, Attendance!I2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2">
+        <f>_xlfn.IFS(Attendance!J2="P", 5, Attendance!J2="O",3,Attendance!J2="A",0, Attendance!J2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K2">
+        <f>_xlfn.IFS(Attendance!K2="P", 5, Attendance!K2="O",3,Attendance!K2="A",0, Attendance!K2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L2">
+        <f>_xlfn.IFS(Attendance!L2="P", 5, Attendance!L2="O",3,Attendance!L2="A",0, Attendance!L2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M2">
+        <f>_xlfn.IFS(Attendance!M2="P", 5, Attendance!M2="O",3,Attendance!M2="A",0, Attendance!M2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N2">
+        <f>_xlfn.IFS(Attendance!N2="P", 5, Attendance!N2="O",3,Attendance!N2="A",0, Attendance!N2="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O2">
+        <f>_xlfn.IFS(Attendance!O2="P", 5, Attendance!O2="O",3,Attendance!O2="A",0, Attendance!O2="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="P2">
+        <f>_xlfn.IFS(Attendance!P2="P", 5, Attendance!P2="O",3,Attendance!P2="A",0, Attendance!P2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q2">
+        <f>_xlfn.IFS(Attendance!Q2="P", 5, Attendance!Q2="O",3,Attendance!Q2="A",0, Attendance!Q2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R2">
+        <f>_xlfn.IFS(Attendance!R2="P", 5, Attendance!R2="O",3,Attendance!R2="A",0, Attendance!R2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="S2">
+        <f>_xlfn.IFS(Attendance!S2="P", 5, Attendance!S2="O",3,Attendance!S2="A",0, Attendance!S2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T2">
+        <f>_xlfn.IFS(Attendance!T2="P", 5, Attendance!T2="O",3,Attendance!T2="A",0, Attendance!T2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="U2">
+        <f>_xlfn.IFS(Attendance!U2="P", 5, Attendance!U2="O",3,Attendance!U2="A",0, Attendance!U2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="V2">
+        <f>_xlfn.IFS(Attendance!V2="P", 5, Attendance!V2="O",3,Attendance!V2="A",0, Attendance!V2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="W2">
+        <f>_xlfn.IFS(Attendance!W2="P", 5, Attendance!W2="O",3,Attendance!W2="A",0, Attendance!W2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X2">
+        <f>_xlfn.IFS(Attendance!X2="P", 5, Attendance!X2="O",3,Attendance!X2="A",0, Attendance!X2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y2">
+        <f>_xlfn.IFS(Attendance!Y2="P", 5, Attendance!Y2="O",3,Attendance!Y2="A",0, Attendance!Y2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z2">
+        <f>_xlfn.IFS(Attendance!Z2="P", 5, Attendance!Z2="O",3,Attendance!Z2="A",0, Attendance!Z2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA2">
+        <f>_xlfn.IFS(Attendance!AA2="P", 5, Attendance!AA2="O",3,Attendance!AA2="A",0, Attendance!AA2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB2">
+        <f>_xlfn.IFS(Attendance!AB2="P", 5, Attendance!AB2="O",3,Attendance!AB2="A",0, Attendance!AB2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC2">
+        <f>_xlfn.IFS(Attendance!AC2="P", 5, Attendance!AC2="O",3,Attendance!AC2="A",0, Attendance!AC2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD2">
+        <f>_xlfn.IFS(Attendance!AD2="P", 5, Attendance!AD2="O",3,Attendance!AD2="A",0, Attendance!AD2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE2">
+        <f>_xlfn.IFS(Attendance!AE2="P", 5, Attendance!AE2="O",3,Attendance!AE2="A",0, Attendance!AE2="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF2">
+        <f>_xlfn.IFS(Attendance!AF2="P", 5, Attendance!AF2="O",3,Attendance!AF2="A",0, Attendance!AF2="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <f>_xlfn.IFS(Attendance!B3="P", 5, Attendance!B3="O",3,Attendance!B3="A",0, Attendance!B3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C3">
+        <f>_xlfn.IFS(Attendance!C3="P", 5, Attendance!C3="O",3,Attendance!C3="A",0, Attendance!C3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D3">
+        <f>_xlfn.IFS(Attendance!D3="P", 5, Attendance!D3="O",3,Attendance!D3="A",0, Attendance!D3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f>_xlfn.IFS(Attendance!E3="P", 5, Attendance!E3="O",3,Attendance!E3="A",0, Attendance!E3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F3">
+        <f>_xlfn.IFS(Attendance!F3="P", 5, Attendance!F3="O",3,Attendance!F3="A",0, Attendance!F3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G3">
+        <f>_xlfn.IFS(Attendance!G3="P", 5, Attendance!G3="O",3,Attendance!G3="A",0, Attendance!G3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H3">
+        <f>_xlfn.IFS(Attendance!H3="P", 5, Attendance!H3="O",3,Attendance!H3="A",0, Attendance!H3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I3">
+        <f>_xlfn.IFS(Attendance!I3="P", 5, Attendance!I3="O",3,Attendance!I3="A",0, Attendance!I3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3">
+        <f>_xlfn.IFS(Attendance!J3="P", 5, Attendance!J3="O",3,Attendance!J3="A",0, Attendance!J3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K3">
+        <f>_xlfn.IFS(Attendance!K3="P", 5, Attendance!K3="O",3,Attendance!K3="A",0, Attendance!K3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L3">
+        <f>_xlfn.IFS(Attendance!L3="P", 5, Attendance!L3="O",3,Attendance!L3="A",0, Attendance!L3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M3">
+        <f>_xlfn.IFS(Attendance!M3="P", 5, Attendance!M3="O",3,Attendance!M3="A",0, Attendance!M3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N3">
+        <f>_xlfn.IFS(Attendance!N3="P", 5, Attendance!N3="O",3,Attendance!N3="A",0, Attendance!N3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O3">
+        <f>_xlfn.IFS(Attendance!O3="P", 5, Attendance!O3="O",3,Attendance!O3="A",0, Attendance!O3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P3">
+        <f>_xlfn.IFS(Attendance!P3="P", 5, Attendance!P3="O",3,Attendance!P3="A",0, Attendance!P3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q3">
+        <f>_xlfn.IFS(Attendance!Q3="P", 5, Attendance!Q3="O",3,Attendance!Q3="A",0, Attendance!Q3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R3">
+        <f>_xlfn.IFS(Attendance!R3="P", 5, Attendance!R3="O",3,Attendance!R3="A",0, Attendance!R3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="S3">
+        <f>_xlfn.IFS(Attendance!S3="P", 5, Attendance!S3="O",3,Attendance!S3="A",0, Attendance!S3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T3">
+        <f>_xlfn.IFS(Attendance!T3="P", 5, Attendance!T3="O",3,Attendance!T3="A",0, Attendance!T3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="U3">
+        <f>_xlfn.IFS(Attendance!U3="P", 5, Attendance!U3="O",3,Attendance!U3="A",0, Attendance!U3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="V3">
+        <f>_xlfn.IFS(Attendance!V3="P", 5, Attendance!V3="O",3,Attendance!V3="A",0, Attendance!V3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="W3">
+        <f>_xlfn.IFS(Attendance!W3="P", 5, Attendance!W3="O",3,Attendance!W3="A",0, Attendance!W3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <f>_xlfn.IFS(Attendance!X3="P", 5, Attendance!X3="O",3,Attendance!X3="A",0, Attendance!X3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y3">
+        <f>_xlfn.IFS(Attendance!Y3="P", 5, Attendance!Y3="O",3,Attendance!Y3="A",0, Attendance!Y3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z3">
+        <f>_xlfn.IFS(Attendance!Z3="P", 5, Attendance!Z3="O",3,Attendance!Z3="A",0, Attendance!Z3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA3">
+        <f>_xlfn.IFS(Attendance!AA3="P", 5, Attendance!AA3="O",3,Attendance!AA3="A",0, Attendance!AA3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AB3">
+        <f>_xlfn.IFS(Attendance!AB3="P", 5, Attendance!AB3="O",3,Attendance!AB3="A",0, Attendance!AB3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AC3">
+        <f>_xlfn.IFS(Attendance!AC3="P", 5, Attendance!AC3="O",3,Attendance!AC3="A",0, Attendance!AC3="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AD3">
+        <f>_xlfn.IFS(Attendance!AD3="P", 5, Attendance!AD3="O",3,Attendance!AD3="A",0, Attendance!AD3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE3">
+        <f>_xlfn.IFS(Attendance!AE3="P", 5, Attendance!AE3="O",3,Attendance!AE3="A",0, Attendance!AE3="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF3">
+        <f>_xlfn.IFS(Attendance!AF3="P", 5, Attendance!AF3="O",3,Attendance!AF3="A",0, Attendance!AF3="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <f>_xlfn.IFS(Attendance!B4="P", 5, Attendance!B4="O",3,Attendance!B4="A",0, Attendance!B4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <f>_xlfn.IFS(Attendance!C4="P", 5, Attendance!C4="O",3,Attendance!C4="A",0, Attendance!C4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D4">
+        <f>_xlfn.IFS(Attendance!D4="P", 5, Attendance!D4="O",3,Attendance!D4="A",0, Attendance!D4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E4">
+        <f>_xlfn.IFS(Attendance!E4="P", 5, Attendance!E4="O",3,Attendance!E4="A",0, Attendance!E4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F4">
+        <f>_xlfn.IFS(Attendance!F4="P", 5, Attendance!F4="O",3,Attendance!F4="A",0, Attendance!F4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G4">
+        <f>_xlfn.IFS(Attendance!G4="P", 5, Attendance!G4="O",3,Attendance!G4="A",0, Attendance!G4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <f>_xlfn.IFS(Attendance!H4="P", 5, Attendance!H4="O",3,Attendance!H4="A",0, Attendance!H4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I4">
+        <f>_xlfn.IFS(Attendance!I4="P", 5, Attendance!I4="O",3,Attendance!I4="A",0, Attendance!I4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J4">
+        <f>_xlfn.IFS(Attendance!J4="P", 5, Attendance!J4="O",3,Attendance!J4="A",0, Attendance!J4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K4">
+        <f>_xlfn.IFS(Attendance!K4="P", 5, Attendance!K4="O",3,Attendance!K4="A",0, Attendance!K4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L4">
+        <f>_xlfn.IFS(Attendance!L4="P", 5, Attendance!L4="O",3,Attendance!L4="A",0, Attendance!L4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M4">
+        <f>_xlfn.IFS(Attendance!M4="P", 5, Attendance!M4="O",3,Attendance!M4="A",0, Attendance!M4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N4">
+        <f>_xlfn.IFS(Attendance!N4="P", 5, Attendance!N4="O",3,Attendance!N4="A",0, Attendance!N4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O4">
+        <f>_xlfn.IFS(Attendance!O4="P", 5, Attendance!O4="O",3,Attendance!O4="A",0, Attendance!O4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P4">
+        <f>_xlfn.IFS(Attendance!P4="P", 5, Attendance!P4="O",3,Attendance!P4="A",0, Attendance!P4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q4">
+        <f>_xlfn.IFS(Attendance!Q4="P", 5, Attendance!Q4="O",3,Attendance!Q4="A",0, Attendance!Q4="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R4">
+        <f>_xlfn.IFS(Attendance!R4="P", 5, Attendance!R4="O",3,Attendance!R4="A",0, Attendance!R4="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="S4">
+        <f>_xlfn.IFS(Attendance!S4="P", 5, Attendance!S4="O",3,Attendance!S4="A",0, Attendance!S4="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T4">
+        <f>_xlfn.IFS(Attendance!T4="P", 5, Attendance!T4="O",3,Attendance!T4="A",0, Attendance!T4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="U4">
+        <f>_xlfn.IFS(Attendance!U4="P", 5, Attendance!U4="O",3,Attendance!U4="A",0, Attendance!U4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V4">
+        <f>_xlfn.IFS(Attendance!V4="P", 5, Attendance!V4="O",3,Attendance!V4="A",0, Attendance!V4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="W4">
+        <f>_xlfn.IFS(Attendance!W4="P", 5, Attendance!W4="O",3,Attendance!W4="A",0, Attendance!W4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X4">
+        <f>_xlfn.IFS(Attendance!X4="P", 5, Attendance!X4="O",3,Attendance!X4="A",0, Attendance!X4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y4">
+        <f>_xlfn.IFS(Attendance!Y4="P", 5, Attendance!Y4="O",3,Attendance!Y4="A",0, Attendance!Y4="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Z4">
+        <f>_xlfn.IFS(Attendance!Z4="P", 5, Attendance!Z4="O",3,Attendance!Z4="A",0, Attendance!Z4="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA4">
+        <f>_xlfn.IFS(Attendance!AA4="P", 5, Attendance!AA4="O",3,Attendance!AA4="A",0, Attendance!AA4="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AB4">
+        <f>_xlfn.IFS(Attendance!AB4="P", 5, Attendance!AB4="O",3,Attendance!AB4="A",0, Attendance!AB4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC4">
+        <f>_xlfn.IFS(Attendance!AC4="P", 5, Attendance!AC4="O",3,Attendance!AC4="A",0, Attendance!AC4="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD4">
+        <f>_xlfn.IFS(Attendance!AD4="P", 5, Attendance!AD4="O",3,Attendance!AD4="A",0, Attendance!AD4="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AE4">
+        <f>_xlfn.IFS(Attendance!AE4="P", 5, Attendance!AE4="O",3,Attendance!AE4="A",0, Attendance!AE4="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AF4">
+        <f>_xlfn.IFS(Attendance!AF4="P", 5, Attendance!AF4="O",3,Attendance!AF4="A",0, Attendance!AF4="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <f>_xlfn.IFS(Attendance!B5="P", 5, Attendance!B5="O",3,Attendance!B5="A",0, Attendance!B5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C5">
+        <f>_xlfn.IFS(Attendance!C5="P", 5, Attendance!C5="O",3,Attendance!C5="A",0, Attendance!C5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D5">
+        <f>_xlfn.IFS(Attendance!D5="P", 5, Attendance!D5="O",3,Attendance!D5="A",0, Attendance!D5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f>_xlfn.IFS(Attendance!E5="P", 5, Attendance!E5="O",3,Attendance!E5="A",0, Attendance!E5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <f>_xlfn.IFS(Attendance!F5="P", 5, Attendance!F5="O",3,Attendance!F5="A",0, Attendance!F5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G5">
+        <f>_xlfn.IFS(Attendance!G5="P", 5, Attendance!G5="O",3,Attendance!G5="A",0, Attendance!G5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H5">
+        <f>_xlfn.IFS(Attendance!H5="P", 5, Attendance!H5="O",3,Attendance!H5="A",0, Attendance!H5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I5">
+        <f>_xlfn.IFS(Attendance!I5="P", 5, Attendance!I5="O",3,Attendance!I5="A",0, Attendance!I5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J5">
+        <f>_xlfn.IFS(Attendance!J5="P", 5, Attendance!J5="O",3,Attendance!J5="A",0, Attendance!J5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K5">
+        <f>_xlfn.IFS(Attendance!K5="P", 5, Attendance!K5="O",3,Attendance!K5="A",0, Attendance!K5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L5">
+        <f>_xlfn.IFS(Attendance!L5="P", 5, Attendance!L5="O",3,Attendance!L5="A",0, Attendance!L5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M5">
+        <f>_xlfn.IFS(Attendance!M5="P", 5, Attendance!M5="O",3,Attendance!M5="A",0, Attendance!M5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N5">
+        <f>_xlfn.IFS(Attendance!N5="P", 5, Attendance!N5="O",3,Attendance!N5="A",0, Attendance!N5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O5">
+        <f>_xlfn.IFS(Attendance!O5="P", 5, Attendance!O5="O",3,Attendance!O5="A",0, Attendance!O5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P5">
+        <f>_xlfn.IFS(Attendance!P5="P", 5, Attendance!P5="O",3,Attendance!P5="A",0, Attendance!P5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q5">
+        <f>_xlfn.IFS(Attendance!Q5="P", 5, Attendance!Q5="O",3,Attendance!Q5="A",0, Attendance!Q5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R5">
+        <f>_xlfn.IFS(Attendance!R5="P", 5, Attendance!R5="O",3,Attendance!R5="A",0, Attendance!R5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <f>_xlfn.IFS(Attendance!S5="P", 5, Attendance!S5="O",3,Attendance!S5="A",0, Attendance!S5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T5">
+        <f>_xlfn.IFS(Attendance!T5="P", 5, Attendance!T5="O",3,Attendance!T5="A",0, Attendance!T5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="U5">
+        <f>_xlfn.IFS(Attendance!U5="P", 5, Attendance!U5="O",3,Attendance!U5="A",0, Attendance!U5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="V5">
+        <f>_xlfn.IFS(Attendance!V5="P", 5, Attendance!V5="O",3,Attendance!V5="A",0, Attendance!V5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="W5">
+        <f>_xlfn.IFS(Attendance!W5="P", 5, Attendance!W5="O",3,Attendance!W5="A",0, Attendance!W5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <f>_xlfn.IFS(Attendance!X5="P", 5, Attendance!X5="O",3,Attendance!X5="A",0, Attendance!X5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Y5">
+        <f>_xlfn.IFS(Attendance!Y5="P", 5, Attendance!Y5="O",3,Attendance!Y5="A",0, Attendance!Y5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z5">
+        <f>_xlfn.IFS(Attendance!Z5="P", 5, Attendance!Z5="O",3,Attendance!Z5="A",0, Attendance!Z5="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA5">
+        <f>_xlfn.IFS(Attendance!AA5="P", 5, Attendance!AA5="O",3,Attendance!AA5="A",0, Attendance!AA5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB5">
+        <f>_xlfn.IFS(Attendance!AB5="P", 5, Attendance!AB5="O",3,Attendance!AB5="A",0, Attendance!AB5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC5">
+        <f>_xlfn.IFS(Attendance!AC5="P", 5, Attendance!AC5="O",3,Attendance!AC5="A",0, Attendance!AC5="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD5">
+        <f>_xlfn.IFS(Attendance!AD5="P", 5, Attendance!AD5="O",3,Attendance!AD5="A",0, Attendance!AD5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AE5">
+        <f>_xlfn.IFS(Attendance!AE5="P", 5, Attendance!AE5="O",3,Attendance!AE5="A",0, Attendance!AE5="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AF5">
+        <f>_xlfn.IFS(Attendance!AF5="P", 5, Attendance!AF5="O",3,Attendance!AF5="A",0, Attendance!AF5="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <f>_xlfn.IFS(Attendance!B6="P", 5, Attendance!B6="O",3,Attendance!B6="A",0, Attendance!B6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C6">
+        <f>_xlfn.IFS(Attendance!C6="P", 5, Attendance!C6="O",3,Attendance!C6="A",0, Attendance!C6="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D6">
+        <f>_xlfn.IFS(Attendance!D6="P", 5, Attendance!D6="O",3,Attendance!D6="A",0, Attendance!D6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E6">
+        <f>_xlfn.IFS(Attendance!E6="P", 5, Attendance!E6="O",3,Attendance!E6="A",0, Attendance!E6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <f>_xlfn.IFS(Attendance!F6="P", 5, Attendance!F6="O",3,Attendance!F6="A",0, Attendance!F6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G6">
+        <f>_xlfn.IFS(Attendance!G6="P", 5, Attendance!G6="O",3,Attendance!G6="A",0, Attendance!G6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H6">
+        <f>_xlfn.IFS(Attendance!H6="P", 5, Attendance!H6="O",3,Attendance!H6="A",0, Attendance!H6="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I6">
+        <f>_xlfn.IFS(Attendance!I6="P", 5, Attendance!I6="O",3,Attendance!I6="A",0, Attendance!I6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J6">
+        <f>_xlfn.IFS(Attendance!J6="P", 5, Attendance!J6="O",3,Attendance!J6="A",0, Attendance!J6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K6">
+        <f>_xlfn.IFS(Attendance!K6="P", 5, Attendance!K6="O",3,Attendance!K6="A",0, Attendance!K6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L6">
+        <f>_xlfn.IFS(Attendance!L6="P", 5, Attendance!L6="O",3,Attendance!L6="A",0, Attendance!L6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M6">
+        <f>_xlfn.IFS(Attendance!M6="P", 5, Attendance!M6="O",3,Attendance!M6="A",0, Attendance!M6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N6">
+        <f>_xlfn.IFS(Attendance!N6="P", 5, Attendance!N6="O",3,Attendance!N6="A",0, Attendance!N6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O6">
+        <f>_xlfn.IFS(Attendance!O6="P", 5, Attendance!O6="O",3,Attendance!O6="A",0, Attendance!O6="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P6">
+        <f>_xlfn.IFS(Attendance!P6="P", 5, Attendance!P6="O",3,Attendance!P6="A",0, Attendance!P6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q6">
+        <f>_xlfn.IFS(Attendance!Q6="P", 5, Attendance!Q6="O",3,Attendance!Q6="A",0, Attendance!Q6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R6">
+        <f>_xlfn.IFS(Attendance!R6="P", 5, Attendance!R6="O",3,Attendance!R6="A",0, Attendance!R6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S6">
+        <f>_xlfn.IFS(Attendance!S6="P", 5, Attendance!S6="O",3,Attendance!S6="A",0, Attendance!S6="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T6">
+        <f>_xlfn.IFS(Attendance!T6="P", 5, Attendance!T6="O",3,Attendance!T6="A",0, Attendance!T6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U6">
+        <f>_xlfn.IFS(Attendance!U6="P", 5, Attendance!U6="O",3,Attendance!U6="A",0, Attendance!U6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V6">
+        <f>_xlfn.IFS(Attendance!V6="P", 5, Attendance!V6="O",3,Attendance!V6="A",0, Attendance!V6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="W6">
+        <f>_xlfn.IFS(Attendance!W6="P", 5, Attendance!W6="O",3,Attendance!W6="A",0, Attendance!W6="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <f>_xlfn.IFS(Attendance!X6="P", 5, Attendance!X6="O",3,Attendance!X6="A",0, Attendance!X6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y6">
+        <f>_xlfn.IFS(Attendance!Y6="P", 5, Attendance!Y6="O",3,Attendance!Y6="A",0, Attendance!Y6="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z6">
+        <f>_xlfn.IFS(Attendance!Z6="P", 5, Attendance!Z6="O",3,Attendance!Z6="A",0, Attendance!Z6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AA6">
+        <f>_xlfn.IFS(Attendance!AA6="P", 5, Attendance!AA6="O",3,Attendance!AA6="A",0, Attendance!AA6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AB6">
+        <f>_xlfn.IFS(Attendance!AB6="P", 5, Attendance!AB6="O",3,Attendance!AB6="A",0, Attendance!AB6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC6">
+        <f>_xlfn.IFS(Attendance!AC6="P", 5, Attendance!AC6="O",3,Attendance!AC6="A",0, Attendance!AC6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AD6">
+        <f>_xlfn.IFS(Attendance!AD6="P", 5, Attendance!AD6="O",3,Attendance!AD6="A",0, Attendance!AD6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AE6">
+        <f>_xlfn.IFS(Attendance!AE6="P", 5, Attendance!AE6="O",3,Attendance!AE6="A",0, Attendance!AE6="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AF6">
+        <f>_xlfn.IFS(Attendance!AF6="P", 5, Attendance!AF6="O",3,Attendance!AF6="A",0, Attendance!AF6="N/A",0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>_xlfn.IFS(Attendance!B7="P", 5, Attendance!B7="O",3,Attendance!B7="A",0, Attendance!B7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C7">
+        <f>_xlfn.IFS(Attendance!C7="P", 5, Attendance!C7="O",3,Attendance!C7="A",0, Attendance!C7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D7">
+        <f>_xlfn.IFS(Attendance!D7="P", 5, Attendance!D7="O",3,Attendance!D7="A",0, Attendance!D7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E7">
+        <f>_xlfn.IFS(Attendance!E7="P", 5, Attendance!E7="O",3,Attendance!E7="A",0, Attendance!E7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F7">
+        <f>_xlfn.IFS(Attendance!F7="P", 5, Attendance!F7="O",3,Attendance!F7="A",0, Attendance!F7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G7">
+        <f>_xlfn.IFS(Attendance!G7="P", 5, Attendance!G7="O",3,Attendance!G7="A",0, Attendance!G7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H7">
+        <f>_xlfn.IFS(Attendance!H7="P", 5, Attendance!H7="O",3,Attendance!H7="A",0, Attendance!H7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I7">
+        <f>_xlfn.IFS(Attendance!I7="P", 5, Attendance!I7="O",3,Attendance!I7="A",0, Attendance!I7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <f>_xlfn.IFS(Attendance!J7="P", 5, Attendance!J7="O",3,Attendance!J7="A",0, Attendance!J7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K7">
+        <f>_xlfn.IFS(Attendance!K7="P", 5, Attendance!K7="O",3,Attendance!K7="A",0, Attendance!K7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L7">
+        <f>_xlfn.IFS(Attendance!L7="P", 5, Attendance!L7="O",3,Attendance!L7="A",0, Attendance!L7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M7">
+        <f>_xlfn.IFS(Attendance!M7="P", 5, Attendance!M7="O",3,Attendance!M7="A",0, Attendance!M7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N7">
+        <f>_xlfn.IFS(Attendance!N7="P", 5, Attendance!N7="O",3,Attendance!N7="A",0, Attendance!N7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O7">
+        <f>_xlfn.IFS(Attendance!O7="P", 5, Attendance!O7="O",3,Attendance!O7="A",0, Attendance!O7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P7">
+        <f>_xlfn.IFS(Attendance!P7="P", 5, Attendance!P7="O",3,Attendance!P7="A",0, Attendance!P7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Q7">
+        <f>_xlfn.IFS(Attendance!Q7="P", 5, Attendance!Q7="O",3,Attendance!Q7="A",0, Attendance!Q7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R7">
+        <f>_xlfn.IFS(Attendance!R7="P", 5, Attendance!R7="O",3,Attendance!R7="A",0, Attendance!R7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="S7">
+        <f>_xlfn.IFS(Attendance!S7="P", 5, Attendance!S7="O",3,Attendance!S7="A",0, Attendance!S7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T7">
+        <f>_xlfn.IFS(Attendance!T7="P", 5, Attendance!T7="O",3,Attendance!T7="A",0, Attendance!T7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="U7">
+        <f>_xlfn.IFS(Attendance!U7="P", 5, Attendance!U7="O",3,Attendance!U7="A",0, Attendance!U7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V7">
+        <f>_xlfn.IFS(Attendance!V7="P", 5, Attendance!V7="O",3,Attendance!V7="A",0, Attendance!V7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="W7">
+        <f>_xlfn.IFS(Attendance!W7="P", 5, Attendance!W7="O",3,Attendance!W7="A",0, Attendance!W7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X7">
+        <f>_xlfn.IFS(Attendance!X7="P", 5, Attendance!X7="O",3,Attendance!X7="A",0, Attendance!X7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y7">
+        <f>_xlfn.IFS(Attendance!Y7="P", 5, Attendance!Y7="O",3,Attendance!Y7="A",0, Attendance!Y7="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z7">
+        <f>_xlfn.IFS(Attendance!Z7="P", 5, Attendance!Z7="O",3,Attendance!Z7="A",0, Attendance!Z7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA7">
+        <f>_xlfn.IFS(Attendance!AA7="P", 5, Attendance!AA7="O",3,Attendance!AA7="A",0, Attendance!AA7="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AB7">
+        <f>_xlfn.IFS(Attendance!AB7="P", 5, Attendance!AB7="O",3,Attendance!AB7="A",0, Attendance!AB7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC7">
+        <f>_xlfn.IFS(Attendance!AC7="P", 5, Attendance!AC7="O",3,Attendance!AC7="A",0, Attendance!AC7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD7">
+        <f>_xlfn.IFS(Attendance!AD7="P", 5, Attendance!AD7="O",3,Attendance!AD7="A",0, Attendance!AD7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE7">
+        <f>_xlfn.IFS(Attendance!AE7="P", 5, Attendance!AE7="O",3,Attendance!AE7="A",0, Attendance!AE7="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF7">
+        <f>_xlfn.IFS(Attendance!AF7="P", 5, Attendance!AF7="O",3,Attendance!AF7="A",0, Attendance!AF7="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <f>_xlfn.IFS(Attendance!B8="P", 5, Attendance!B8="O",3,Attendance!B8="A",0, Attendance!B8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C8">
+        <f>_xlfn.IFS(Attendance!C8="P", 5, Attendance!C8="O",3,Attendance!C8="A",0, Attendance!C8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D8">
+        <f>_xlfn.IFS(Attendance!D8="P", 5, Attendance!D8="O",3,Attendance!D8="A",0, Attendance!D8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E8">
+        <f>_xlfn.IFS(Attendance!E8="P", 5, Attendance!E8="O",3,Attendance!E8="A",0, Attendance!E8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <f>_xlfn.IFS(Attendance!F8="P", 5, Attendance!F8="O",3,Attendance!F8="A",0, Attendance!F8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G8">
+        <f>_xlfn.IFS(Attendance!G8="P", 5, Attendance!G8="O",3,Attendance!G8="A",0, Attendance!G8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H8">
+        <f>_xlfn.IFS(Attendance!H8="P", 5, Attendance!H8="O",3,Attendance!H8="A",0, Attendance!H8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I8">
+        <f>_xlfn.IFS(Attendance!I8="P", 5, Attendance!I8="O",3,Attendance!I8="A",0, Attendance!I8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J8">
+        <f>_xlfn.IFS(Attendance!J8="P", 5, Attendance!J8="O",3,Attendance!J8="A",0, Attendance!J8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K8">
+        <f>_xlfn.IFS(Attendance!K8="P", 5, Attendance!K8="O",3,Attendance!K8="A",0, Attendance!K8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L8">
+        <f>_xlfn.IFS(Attendance!L8="P", 5, Attendance!L8="O",3,Attendance!L8="A",0, Attendance!L8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M8">
+        <f>_xlfn.IFS(Attendance!M8="P", 5, Attendance!M8="O",3,Attendance!M8="A",0, Attendance!M8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N8">
+        <f>_xlfn.IFS(Attendance!N8="P", 5, Attendance!N8="O",3,Attendance!N8="A",0, Attendance!N8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O8">
+        <f>_xlfn.IFS(Attendance!O8="P", 5, Attendance!O8="O",3,Attendance!O8="A",0, Attendance!O8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P8">
+        <f>_xlfn.IFS(Attendance!P8="P", 5, Attendance!P8="O",3,Attendance!P8="A",0, Attendance!P8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q8">
+        <f>_xlfn.IFS(Attendance!Q8="P", 5, Attendance!Q8="O",3,Attendance!Q8="A",0, Attendance!Q8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R8">
+        <f>_xlfn.IFS(Attendance!R8="P", 5, Attendance!R8="O",3,Attendance!R8="A",0, Attendance!R8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="S8">
+        <f>_xlfn.IFS(Attendance!S8="P", 5, Attendance!S8="O",3,Attendance!S8="A",0, Attendance!S8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T8">
+        <f>_xlfn.IFS(Attendance!T8="P", 5, Attendance!T8="O",3,Attendance!T8="A",0, Attendance!T8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U8">
+        <f>_xlfn.IFS(Attendance!U8="P", 5, Attendance!U8="O",3,Attendance!U8="A",0, Attendance!U8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="V8">
+        <f>_xlfn.IFS(Attendance!V8="P", 5, Attendance!V8="O",3,Attendance!V8="A",0, Attendance!V8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="W8">
+        <f>_xlfn.IFS(Attendance!W8="P", 5, Attendance!W8="O",3,Attendance!W8="A",0, Attendance!W8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X8">
+        <f>_xlfn.IFS(Attendance!X8="P", 5, Attendance!X8="O",3,Attendance!X8="A",0, Attendance!X8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y8">
+        <f>_xlfn.IFS(Attendance!Y8="P", 5, Attendance!Y8="O",3,Attendance!Y8="A",0, Attendance!Y8="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z8">
+        <f>_xlfn.IFS(Attendance!Z8="P", 5, Attendance!Z8="O",3,Attendance!Z8="A",0, Attendance!Z8="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA8">
+        <f>_xlfn.IFS(Attendance!AA8="P", 5, Attendance!AA8="O",3,Attendance!AA8="A",0, Attendance!AA8="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB8">
+        <f>_xlfn.IFS(Attendance!AB8="P", 5, Attendance!AB8="O",3,Attendance!AB8="A",0, Attendance!AB8="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC8">
+        <f>_xlfn.IFS(Attendance!AC8="P", 5, Attendance!AC8="O",3,Attendance!AC8="A",0, Attendance!AC8="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD8">
+        <f>_xlfn.IFS(Attendance!AD8="P", 5, Attendance!AD8="O",3,Attendance!AD8="A",0, Attendance!AD8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AE8">
+        <f>_xlfn.IFS(Attendance!AE8="P", 5, Attendance!AE8="O",3,Attendance!AE8="A",0, Attendance!AE8="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AF8">
+        <f>_xlfn.IFS(Attendance!AF8="P", 5, Attendance!AF8="O",3,Attendance!AF8="A",0, Attendance!AF8="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <f>_xlfn.IFS(Attendance!B9="P", 5, Attendance!B9="O",3,Attendance!B9="A",0, Attendance!B9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C9">
+        <f>_xlfn.IFS(Attendance!C9="P", 5, Attendance!C9="O",3,Attendance!C9="A",0, Attendance!C9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <f>_xlfn.IFS(Attendance!D9="P", 5, Attendance!D9="O",3,Attendance!D9="A",0, Attendance!D9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E9">
+        <f>_xlfn.IFS(Attendance!E9="P", 5, Attendance!E9="O",3,Attendance!E9="A",0, Attendance!E9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="F9">
+        <f>_xlfn.IFS(Attendance!F9="P", 5, Attendance!F9="O",3,Attendance!F9="A",0, Attendance!F9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G9">
+        <f>_xlfn.IFS(Attendance!G9="P", 5, Attendance!G9="O",3,Attendance!G9="A",0, Attendance!G9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H9">
+        <f>_xlfn.IFS(Attendance!H9="P", 5, Attendance!H9="O",3,Attendance!H9="A",0, Attendance!H9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I9">
+        <f>_xlfn.IFS(Attendance!I9="P", 5, Attendance!I9="O",3,Attendance!I9="A",0, Attendance!I9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9">
+        <f>_xlfn.IFS(Attendance!J9="P", 5, Attendance!J9="O",3,Attendance!J9="A",0, Attendance!J9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K9">
+        <f>_xlfn.IFS(Attendance!K9="P", 5, Attendance!K9="O",3,Attendance!K9="A",0, Attendance!K9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L9">
+        <f>_xlfn.IFS(Attendance!L9="P", 5, Attendance!L9="O",3,Attendance!L9="A",0, Attendance!L9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M9">
+        <f>_xlfn.IFS(Attendance!M9="P", 5, Attendance!M9="O",3,Attendance!M9="A",0, Attendance!M9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N9">
+        <f>_xlfn.IFS(Attendance!N9="P", 5, Attendance!N9="O",3,Attendance!N9="A",0, Attendance!N9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O9">
+        <f>_xlfn.IFS(Attendance!O9="P", 5, Attendance!O9="O",3,Attendance!O9="A",0, Attendance!O9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P9">
+        <f>_xlfn.IFS(Attendance!P9="P", 5, Attendance!P9="O",3,Attendance!P9="A",0, Attendance!P9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Q9">
+        <f>_xlfn.IFS(Attendance!Q9="P", 5, Attendance!Q9="O",3,Attendance!Q9="A",0, Attendance!Q9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R9">
+        <f>_xlfn.IFS(Attendance!R9="P", 5, Attendance!R9="O",3,Attendance!R9="A",0, Attendance!R9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S9">
+        <f>_xlfn.IFS(Attendance!S9="P", 5, Attendance!S9="O",3,Attendance!S9="A",0, Attendance!S9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T9">
+        <f>_xlfn.IFS(Attendance!T9="P", 5, Attendance!T9="O",3,Attendance!T9="A",0, Attendance!T9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="U9">
+        <f>_xlfn.IFS(Attendance!U9="P", 5, Attendance!U9="O",3,Attendance!U9="A",0, Attendance!U9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V9">
+        <f>_xlfn.IFS(Attendance!V9="P", 5, Attendance!V9="O",3,Attendance!V9="A",0, Attendance!V9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="W9">
+        <f>_xlfn.IFS(Attendance!W9="P", 5, Attendance!W9="O",3,Attendance!W9="A",0, Attendance!W9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X9">
+        <f>_xlfn.IFS(Attendance!X9="P", 5, Attendance!X9="O",3,Attendance!X9="A",0, Attendance!X9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y9">
+        <f>_xlfn.IFS(Attendance!Y9="P", 5, Attendance!Y9="O",3,Attendance!Y9="A",0, Attendance!Y9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Z9">
+        <f>_xlfn.IFS(Attendance!Z9="P", 5, Attendance!Z9="O",3,Attendance!Z9="A",0, Attendance!Z9="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA9">
+        <f>_xlfn.IFS(Attendance!AA9="P", 5, Attendance!AA9="O",3,Attendance!AA9="A",0, Attendance!AA9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB9">
+        <f>_xlfn.IFS(Attendance!AB9="P", 5, Attendance!AB9="O",3,Attendance!AB9="A",0, Attendance!AB9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC9">
+        <f>_xlfn.IFS(Attendance!AC9="P", 5, Attendance!AC9="O",3,Attendance!AC9="A",0, Attendance!AC9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD9">
+        <f>_xlfn.IFS(Attendance!AD9="P", 5, Attendance!AD9="O",3,Attendance!AD9="A",0, Attendance!AD9="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE9">
+        <f>_xlfn.IFS(Attendance!AE9="P", 5, Attendance!AE9="O",3,Attendance!AE9="A",0, Attendance!AE9="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AF9">
+        <f>_xlfn.IFS(Attendance!AF9="P", 5, Attendance!AF9="O",3,Attendance!AF9="A",0, Attendance!AF9="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <f>_xlfn.IFS(Attendance!B10="P", 5, Attendance!B10="O",3,Attendance!B10="A",0, Attendance!B10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="C10">
+        <f>_xlfn.IFS(Attendance!C10="P", 5, Attendance!C10="O",3,Attendance!C10="A",0, Attendance!C10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D10">
+        <f>_xlfn.IFS(Attendance!D10="P", 5, Attendance!D10="O",3,Attendance!D10="A",0, Attendance!D10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E10">
+        <f>_xlfn.IFS(Attendance!E10="P", 5, Attendance!E10="O",3,Attendance!E10="A",0, Attendance!E10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="F10">
+        <f>_xlfn.IFS(Attendance!F10="P", 5, Attendance!F10="O",3,Attendance!F10="A",0, Attendance!F10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G10">
+        <f>_xlfn.IFS(Attendance!G10="P", 5, Attendance!G10="O",3,Attendance!G10="A",0, Attendance!G10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H10">
+        <f>_xlfn.IFS(Attendance!H10="P", 5, Attendance!H10="O",3,Attendance!H10="A",0, Attendance!H10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I10">
+        <f>_xlfn.IFS(Attendance!I10="P", 5, Attendance!I10="O",3,Attendance!I10="A",0, Attendance!I10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f>_xlfn.IFS(Attendance!J10="P", 5, Attendance!J10="O",3,Attendance!J10="A",0, Attendance!J10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K10">
+        <f>_xlfn.IFS(Attendance!K10="P", 5, Attendance!K10="O",3,Attendance!K10="A",0, Attendance!K10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L10">
+        <f>_xlfn.IFS(Attendance!L10="P", 5, Attendance!L10="O",3,Attendance!L10="A",0, Attendance!L10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M10">
+        <f>_xlfn.IFS(Attendance!M10="P", 5, Attendance!M10="O",3,Attendance!M10="A",0, Attendance!M10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N10">
+        <f>_xlfn.IFS(Attendance!N10="P", 5, Attendance!N10="O",3,Attendance!N10="A",0, Attendance!N10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O10">
+        <f>_xlfn.IFS(Attendance!O10="P", 5, Attendance!O10="O",3,Attendance!O10="A",0, Attendance!O10="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <f>_xlfn.IFS(Attendance!P10="P", 5, Attendance!P10="O",3,Attendance!P10="A",0, Attendance!P10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q10">
+        <f>_xlfn.IFS(Attendance!Q10="P", 5, Attendance!Q10="O",3,Attendance!Q10="A",0, Attendance!Q10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R10">
+        <f>_xlfn.IFS(Attendance!R10="P", 5, Attendance!R10="O",3,Attendance!R10="A",0, Attendance!R10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S10">
+        <f>_xlfn.IFS(Attendance!S10="P", 5, Attendance!S10="O",3,Attendance!S10="A",0, Attendance!S10="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T10">
+        <f>_xlfn.IFS(Attendance!T10="P", 5, Attendance!T10="O",3,Attendance!T10="A",0, Attendance!T10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U10">
+        <f>_xlfn.IFS(Attendance!U10="P", 5, Attendance!U10="O",3,Attendance!U10="A",0, Attendance!U10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="V10">
+        <f>_xlfn.IFS(Attendance!V10="P", 5, Attendance!V10="O",3,Attendance!V10="A",0, Attendance!V10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="W10">
+        <f>_xlfn.IFS(Attendance!W10="P", 5, Attendance!W10="O",3,Attendance!W10="A",0, Attendance!W10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X10">
+        <f>_xlfn.IFS(Attendance!X10="P", 5, Attendance!X10="O",3,Attendance!X10="A",0, Attendance!X10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y10">
+        <f>_xlfn.IFS(Attendance!Y10="P", 5, Attendance!Y10="O",3,Attendance!Y10="A",0, Attendance!Y10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z10">
+        <f>_xlfn.IFS(Attendance!Z10="P", 5, Attendance!Z10="O",3,Attendance!Z10="A",0, Attendance!Z10="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA10">
+        <f>_xlfn.IFS(Attendance!AA10="P", 5, Attendance!AA10="O",3,Attendance!AA10="A",0, Attendance!AA10="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AB10">
+        <f>_xlfn.IFS(Attendance!AB10="P", 5, Attendance!AB10="O",3,Attendance!AB10="A",0, Attendance!AB10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AC10">
+        <f>_xlfn.IFS(Attendance!AC10="P", 5, Attendance!AC10="O",3,Attendance!AC10="A",0, Attendance!AC10="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD10">
+        <f>_xlfn.IFS(Attendance!AD10="P", 5, Attendance!AD10="O",3,Attendance!AD10="A",0, Attendance!AD10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AE10">
+        <f>_xlfn.IFS(Attendance!AE10="P", 5, Attendance!AE10="O",3,Attendance!AE10="A",0, Attendance!AE10="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="AF10">
+        <f>_xlfn.IFS(Attendance!AF10="P", 5, Attendance!AF10="O",3,Attendance!AF10="A",0, Attendance!AF10="N/A",0)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <f>_xlfn.IFS(Attendance!B11="P", 5, Attendance!B11="O",3,Attendance!B11="A",0, Attendance!B11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C11">
+        <f>_xlfn.IFS(Attendance!C11="P", 5, Attendance!C11="O",3,Attendance!C11="A",0, Attendance!C11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D11">
+        <f>_xlfn.IFS(Attendance!D11="P", 5, Attendance!D11="O",3,Attendance!D11="A",0, Attendance!D11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f>_xlfn.IFS(Attendance!E11="P", 5, Attendance!E11="O",3,Attendance!E11="A",0, Attendance!E11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F11">
+        <f>_xlfn.IFS(Attendance!F11="P", 5, Attendance!F11="O",3,Attendance!F11="A",0, Attendance!F11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G11">
+        <f>_xlfn.IFS(Attendance!G11="P", 5, Attendance!G11="O",3,Attendance!G11="A",0, Attendance!G11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H11">
+        <f>_xlfn.IFS(Attendance!H11="P", 5, Attendance!H11="O",3,Attendance!H11="A",0, Attendance!H11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <f>_xlfn.IFS(Attendance!I11="P", 5, Attendance!I11="O",3,Attendance!I11="A",0, Attendance!I11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J11">
+        <f>_xlfn.IFS(Attendance!J11="P", 5, Attendance!J11="O",3,Attendance!J11="A",0, Attendance!J11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K11">
+        <f>_xlfn.IFS(Attendance!K11="P", 5, Attendance!K11="O",3,Attendance!K11="A",0, Attendance!K11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L11">
+        <f>_xlfn.IFS(Attendance!L11="P", 5, Attendance!L11="O",3,Attendance!L11="A",0, Attendance!L11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M11">
+        <f>_xlfn.IFS(Attendance!M11="P", 5, Attendance!M11="O",3,Attendance!M11="A",0, Attendance!M11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N11">
+        <f>_xlfn.IFS(Attendance!N11="P", 5, Attendance!N11="O",3,Attendance!N11="A",0, Attendance!N11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11">
+        <f>_xlfn.IFS(Attendance!O11="P", 5, Attendance!O11="O",3,Attendance!O11="A",0, Attendance!O11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f>_xlfn.IFS(Attendance!P11="P", 5, Attendance!P11="O",3,Attendance!P11="A",0, Attendance!P11="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Q11">
+        <f>_xlfn.IFS(Attendance!Q11="P", 5, Attendance!Q11="O",3,Attendance!Q11="A",0, Attendance!Q11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R11">
+        <f>_xlfn.IFS(Attendance!R11="P", 5, Attendance!R11="O",3,Attendance!R11="A",0, Attendance!R11="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="S11">
+        <f>_xlfn.IFS(Attendance!S11="P", 5, Attendance!S11="O",3,Attendance!S11="A",0, Attendance!S11="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T11">
+        <f>_xlfn.IFS(Attendance!T11="P", 5, Attendance!T11="O",3,Attendance!T11="A",0, Attendance!T11="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <f>_xlfn.IFS(Attendance!U11="P", 5, Attendance!U11="O",3,Attendance!U11="A",0, Attendance!U11="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="V11">
+        <f>_xlfn.IFS(Attendance!V11="P", 5, Attendance!V11="O",3,Attendance!V11="A",0, Attendance!V11="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="W11">
+        <f>_xlfn.IFS(Attendance!W11="P", 5, Attendance!W11="O",3,Attendance!W11="A",0, Attendance!W11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X11">
+        <f>_xlfn.IFS(Attendance!X11="P", 5, Attendance!X11="O",3,Attendance!X11="A",0, Attendance!X11="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Y11">
+        <f>_xlfn.IFS(Attendance!Y11="P", 5, Attendance!Y11="O",3,Attendance!Y11="A",0, Attendance!Y11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z11">
+        <f>_xlfn.IFS(Attendance!Z11="P", 5, Attendance!Z11="O",3,Attendance!Z11="A",0, Attendance!Z11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA11">
+        <f>_xlfn.IFS(Attendance!AA11="P", 5, Attendance!AA11="O",3,Attendance!AA11="A",0, Attendance!AA11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB11">
+        <f>_xlfn.IFS(Attendance!AB11="P", 5, Attendance!AB11="O",3,Attendance!AB11="A",0, Attendance!AB11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC11">
+        <f>_xlfn.IFS(Attendance!AC11="P", 5, Attendance!AC11="O",3,Attendance!AC11="A",0, Attendance!AC11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD11">
+        <f>_xlfn.IFS(Attendance!AD11="P", 5, Attendance!AD11="O",3,Attendance!AD11="A",0, Attendance!AD11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE11">
+        <f>_xlfn.IFS(Attendance!AE11="P", 5, Attendance!AE11="O",3,Attendance!AE11="A",0, Attendance!AE11="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF11">
+        <f>_xlfn.IFS(Attendance!AF11="P", 5, Attendance!AF11="O",3,Attendance!AF11="A",0, Attendance!AF11="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <f>_xlfn.IFS(Attendance!B12="P", 5, Attendance!B12="O",3,Attendance!B12="A",0, Attendance!B12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C12">
+        <f>_xlfn.IFS(Attendance!C12="P", 5, Attendance!C12="O",3,Attendance!C12="A",0, Attendance!C12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D12">
+        <f>_xlfn.IFS(Attendance!D12="P", 5, Attendance!D12="O",3,Attendance!D12="A",0, Attendance!D12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <f>_xlfn.IFS(Attendance!E12="P", 5, Attendance!E12="O",3,Attendance!E12="A",0, Attendance!E12="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="F12">
+        <f>_xlfn.IFS(Attendance!F12="P", 5, Attendance!F12="O",3,Attendance!F12="A",0, Attendance!F12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G12">
+        <f>_xlfn.IFS(Attendance!G12="P", 5, Attendance!G12="O",3,Attendance!G12="A",0, Attendance!G12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H12">
+        <f>_xlfn.IFS(Attendance!H12="P", 5, Attendance!H12="O",3,Attendance!H12="A",0, Attendance!H12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="I12">
+        <f>_xlfn.IFS(Attendance!I12="P", 5, Attendance!I12="O",3,Attendance!I12="A",0, Attendance!I12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="J12">
+        <f>_xlfn.IFS(Attendance!J12="P", 5, Attendance!J12="O",3,Attendance!J12="A",0, Attendance!J12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="K12">
+        <f>_xlfn.IFS(Attendance!K12="P", 5, Attendance!K12="O",3,Attendance!K12="A",0, Attendance!K12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="L12">
+        <f>_xlfn.IFS(Attendance!L12="P", 5, Attendance!L12="O",3,Attendance!L12="A",0, Attendance!L12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="M12">
+        <f>_xlfn.IFS(Attendance!M12="P", 5, Attendance!M12="O",3,Attendance!M12="A",0, Attendance!M12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="N12">
+        <f>_xlfn.IFS(Attendance!N12="P", 5, Attendance!N12="O",3,Attendance!N12="A",0, Attendance!N12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="O12">
+        <f>_xlfn.IFS(Attendance!O12="P", 5, Attendance!O12="O",3,Attendance!O12="A",0, Attendance!O12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P12">
+        <f>_xlfn.IFS(Attendance!P12="P", 5, Attendance!P12="O",3,Attendance!P12="A",0, Attendance!P12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q12">
+        <f>_xlfn.IFS(Attendance!Q12="P", 5, Attendance!Q12="O",3,Attendance!Q12="A",0, Attendance!Q12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="R12">
+        <f>_xlfn.IFS(Attendance!R12="P", 5, Attendance!R12="O",3,Attendance!R12="A",0, Attendance!R12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S12">
+        <f>_xlfn.IFS(Attendance!S12="P", 5, Attendance!S12="O",3,Attendance!S12="A",0, Attendance!S12="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T12">
+        <f>_xlfn.IFS(Attendance!T12="P", 5, Attendance!T12="O",3,Attendance!T12="A",0, Attendance!T12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U12">
+        <f>_xlfn.IFS(Attendance!U12="P", 5, Attendance!U12="O",3,Attendance!U12="A",0, Attendance!U12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V12">
+        <f>_xlfn.IFS(Attendance!V12="P", 5, Attendance!V12="O",3,Attendance!V12="A",0, Attendance!V12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="W12">
+        <f>_xlfn.IFS(Attendance!W12="P", 5, Attendance!W12="O",3,Attendance!W12="A",0, Attendance!W12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X12">
+        <f>_xlfn.IFS(Attendance!X12="P", 5, Attendance!X12="O",3,Attendance!X12="A",0, Attendance!X12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y12">
+        <f>_xlfn.IFS(Attendance!Y12="P", 5, Attendance!Y12="O",3,Attendance!Y12="A",0, Attendance!Y12="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z12">
+        <f>_xlfn.IFS(Attendance!Z12="P", 5, Attendance!Z12="O",3,Attendance!Z12="A",0, Attendance!Z12="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AA12">
+        <f>_xlfn.IFS(Attendance!AA12="P", 5, Attendance!AA12="O",3,Attendance!AA12="A",0, Attendance!AA12="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="AB12">
+        <f>_xlfn.IFS(Attendance!AB12="P", 5, Attendance!AB12="O",3,Attendance!AB12="A",0, Attendance!AB12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC12">
+        <f>_xlfn.IFS(Attendance!AC12="P", 5, Attendance!AC12="O",3,Attendance!AC12="A",0, Attendance!AC12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD12">
+        <f>_xlfn.IFS(Attendance!AD12="P", 5, Attendance!AD12="O",3,Attendance!AD12="A",0, Attendance!AD12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE12">
+        <f>_xlfn.IFS(Attendance!AE12="P", 5, Attendance!AE12="O",3,Attendance!AE12="A",0, Attendance!AE12="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF12">
+        <f>_xlfn.IFS(Attendance!AF12="P", 5, Attendance!AF12="O",3,Attendance!AF12="A",0, Attendance!AF12="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <f>_xlfn.IFS(Attendance!B13="P", 5, Attendance!B13="O",3,Attendance!B13="A",0, Attendance!B13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C13">
+        <f>_xlfn.IFS(Attendance!C13="P", 5, Attendance!C13="O",3,Attendance!C13="A",0, Attendance!C13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="D13">
+        <f>_xlfn.IFS(Attendance!D13="P", 5, Attendance!D13="O",3,Attendance!D13="A",0, Attendance!D13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="E13">
+        <f>_xlfn.IFS(Attendance!E13="P", 5, Attendance!E13="O",3,Attendance!E13="A",0, Attendance!E13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F13">
+        <f>_xlfn.IFS(Attendance!F13="P", 5, Attendance!F13="O",3,Attendance!F13="A",0, Attendance!F13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="G13">
+        <f>_xlfn.IFS(Attendance!G13="P", 5, Attendance!G13="O",3,Attendance!G13="A",0, Attendance!G13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="H13">
+        <f>_xlfn.IFS(Attendance!H13="P", 5, Attendance!H13="O",3,Attendance!H13="A",0, Attendance!H13="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="I13">
+        <f>_xlfn.IFS(Attendance!I13="P", 5, Attendance!I13="O",3,Attendance!I13="A",0, Attendance!I13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J13">
+        <f>_xlfn.IFS(Attendance!J13="P", 5, Attendance!J13="O",3,Attendance!J13="A",0, Attendance!J13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K13">
+        <f>_xlfn.IFS(Attendance!K13="P", 5, Attendance!K13="O",3,Attendance!K13="A",0, Attendance!K13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L13">
+        <f>_xlfn.IFS(Attendance!L13="P", 5, Attendance!L13="O",3,Attendance!L13="A",0, Attendance!L13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M13">
+        <f>_xlfn.IFS(Attendance!M13="P", 5, Attendance!M13="O",3,Attendance!M13="A",0, Attendance!M13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N13">
+        <f>_xlfn.IFS(Attendance!N13="P", 5, Attendance!N13="O",3,Attendance!N13="A",0, Attendance!N13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O13">
+        <f>_xlfn.IFS(Attendance!O13="P", 5, Attendance!O13="O",3,Attendance!O13="A",0, Attendance!O13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="P13">
+        <f>_xlfn.IFS(Attendance!P13="P", 5, Attendance!P13="O",3,Attendance!P13="A",0, Attendance!P13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Q13">
+        <f>_xlfn.IFS(Attendance!Q13="P", 5, Attendance!Q13="O",3,Attendance!Q13="A",0, Attendance!Q13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="R13">
+        <f>_xlfn.IFS(Attendance!R13="P", 5, Attendance!R13="O",3,Attendance!R13="A",0, Attendance!R13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S13">
+        <f>_xlfn.IFS(Attendance!S13="P", 5, Attendance!S13="O",3,Attendance!S13="A",0, Attendance!S13="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="T13">
+        <f>_xlfn.IFS(Attendance!T13="P", 5, Attendance!T13="O",3,Attendance!T13="A",0, Attendance!T13="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="U13">
+        <f>_xlfn.IFS(Attendance!U13="P", 5, Attendance!U13="O",3,Attendance!U13="A",0, Attendance!U13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="V13">
+        <f>_xlfn.IFS(Attendance!V13="P", 5, Attendance!V13="O",3,Attendance!V13="A",0, Attendance!V13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="W13">
+        <f>_xlfn.IFS(Attendance!W13="P", 5, Attendance!W13="O",3,Attendance!W13="A",0, Attendance!W13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="X13">
+        <f>_xlfn.IFS(Attendance!X13="P", 5, Attendance!X13="O",3,Attendance!X13="A",0, Attendance!X13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Y13">
+        <f>_xlfn.IFS(Attendance!Y13="P", 5, Attendance!Y13="O",3,Attendance!Y13="A",0, Attendance!Y13="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="Z13">
+        <f>_xlfn.IFS(Attendance!Z13="P", 5, Attendance!Z13="O",3,Attendance!Z13="A",0, Attendance!Z13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA13">
+        <f>_xlfn.IFS(Attendance!AA13="P", 5, Attendance!AA13="O",3,Attendance!AA13="A",0, Attendance!AA13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB13">
+        <f>_xlfn.IFS(Attendance!AB13="P", 5, Attendance!AB13="O",3,Attendance!AB13="A",0, Attendance!AB13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC13">
+        <f>_xlfn.IFS(Attendance!AC13="P", 5, Attendance!AC13="O",3,Attendance!AC13="A",0, Attendance!AC13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD13">
+        <f>_xlfn.IFS(Attendance!AD13="P", 5, Attendance!AD13="O",3,Attendance!AD13="A",0, Attendance!AD13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE13">
+        <f>_xlfn.IFS(Attendance!AE13="P", 5, Attendance!AE13="O",3,Attendance!AE13="A",0, Attendance!AE13="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF13">
+        <f>_xlfn.IFS(Attendance!AF13="P", 5, Attendance!AF13="O",3,Attendance!AF13="A",0, Attendance!AF13="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <f>_xlfn.IFS(Attendance!B14="P", 5, Attendance!B14="O",3,Attendance!B14="A",0, Attendance!B14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="C14">
+        <f>_xlfn.IFS(Attendance!C14="P", 5, Attendance!C14="O",3,Attendance!C14="A",0, Attendance!C14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="D14">
+        <f>_xlfn.IFS(Attendance!D14="P", 5, Attendance!D14="O",3,Attendance!D14="A",0, Attendance!D14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f>_xlfn.IFS(Attendance!E14="P", 5, Attendance!E14="O",3,Attendance!E14="A",0, Attendance!E14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="F14">
+        <f>_xlfn.IFS(Attendance!F14="P", 5, Attendance!F14="O",3,Attendance!F14="A",0, Attendance!F14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="G14">
+        <f>_xlfn.IFS(Attendance!G14="P", 5, Attendance!G14="O",3,Attendance!G14="A",0, Attendance!G14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="H14">
+        <f>_xlfn.IFS(Attendance!H14="P", 5, Attendance!H14="O",3,Attendance!H14="A",0, Attendance!H14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="I14">
+        <f>_xlfn.IFS(Attendance!I14="P", 5, Attendance!I14="O",3,Attendance!I14="A",0, Attendance!I14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="J14">
+        <f>_xlfn.IFS(Attendance!J14="P", 5, Attendance!J14="O",3,Attendance!J14="A",0, Attendance!J14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="K14">
+        <f>_xlfn.IFS(Attendance!K14="P", 5, Attendance!K14="O",3,Attendance!K14="A",0, Attendance!K14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="L14">
+        <f>_xlfn.IFS(Attendance!L14="P", 5, Attendance!L14="O",3,Attendance!L14="A",0, Attendance!L14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="M14">
+        <f>_xlfn.IFS(Attendance!M14="P", 5, Attendance!M14="O",3,Attendance!M14="A",0, Attendance!M14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="N14">
+        <f>_xlfn.IFS(Attendance!N14="P", 5, Attendance!N14="O",3,Attendance!N14="A",0, Attendance!N14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="O14">
+        <f>_xlfn.IFS(Attendance!O14="P", 5, Attendance!O14="O",3,Attendance!O14="A",0, Attendance!O14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="P14">
+        <f>_xlfn.IFS(Attendance!P14="P", 5, Attendance!P14="O",3,Attendance!P14="A",0, Attendance!P14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q14">
+        <f>_xlfn.IFS(Attendance!Q14="P", 5, Attendance!Q14="O",3,Attendance!Q14="A",0, Attendance!Q14="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="R14">
+        <f>_xlfn.IFS(Attendance!R14="P", 5, Attendance!R14="O",3,Attendance!R14="A",0, Attendance!R14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="S14">
+        <f>_xlfn.IFS(Attendance!S14="P", 5, Attendance!S14="O",3,Attendance!S14="A",0, Attendance!S14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="T14">
+        <f>_xlfn.IFS(Attendance!T14="P", 5, Attendance!T14="O",3,Attendance!T14="A",0, Attendance!T14="N/A",0)</f>
+        <v>5</v>
+      </c>
+      <c r="U14">
+        <f>_xlfn.IFS(Attendance!U14="P", 5, Attendance!U14="O",3,Attendance!U14="A",0, Attendance!U14="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="V14">
+        <f>_xlfn.IFS(Attendance!V14="P", 5, Attendance!V14="O",3,Attendance!V14="A",0, Attendance!V14="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="W14">
+        <f>_xlfn.IFS(Attendance!W14="P", 5, Attendance!W14="O",3,Attendance!W14="A",0, Attendance!W14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="X14">
+        <f>_xlfn.IFS(Attendance!X14="P", 5, Attendance!X14="O",3,Attendance!X14="A",0, Attendance!X14="N/A",0)</f>
+        <v>3</v>
+      </c>
+      <c r="Y14">
+        <f>_xlfn.IFS(Attendance!Y14="P", 5, Attendance!Y14="O",3,Attendance!Y14="A",0, Attendance!Y14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="Z14">
+        <f>_xlfn.IFS(Attendance!Z14="P", 5, Attendance!Z14="O",3,Attendance!Z14="A",0, Attendance!Z14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AA14">
+        <f>_xlfn.IFS(Attendance!AA14="P", 5, Attendance!AA14="O",3,Attendance!AA14="A",0, Attendance!AA14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AB14">
+        <f>_xlfn.IFS(Attendance!AB14="P", 5, Attendance!AB14="O",3,Attendance!AB14="A",0, Attendance!AB14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AC14">
+        <f>_xlfn.IFS(Attendance!AC14="P", 5, Attendance!AC14="O",3,Attendance!AC14="A",0, Attendance!AC14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AD14">
+        <f>_xlfn.IFS(Attendance!AD14="P", 5, Attendance!AD14="O",3,Attendance!AD14="A",0, Attendance!AD14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AE14">
+        <f>_xlfn.IFS(Attendance!AE14="P", 5, Attendance!AE14="O",3,Attendance!AE14="A",0, Attendance!AE14="N/A",0)</f>
+        <v>0</v>
+      </c>
+      <c r="AF14">
+        <f>_xlfn.IFS(Attendance!AF14="P", 5, Attendance!AF14="O",3,Attendance!AF14="A",0, Attendance!AF14="N/A",0)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B78BAD9-C027-4A50-86F1-B5BC62C95462}">
+  <dimension ref="A1:E14"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="24.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.77734375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2">
+        <f>SUM(Sheet2!B2:AF2)</f>
+        <v>49</v>
+      </c>
+      <c r="C2">
+        <f>ROUND(B2*5/155, 2)</f>
+        <v>1.58</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <f>D2*5/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B3">
+        <f>SUM(Sheet2!B3:AF3)</f>
+        <v>12</v>
+      </c>
+      <c r="C3">
+        <f t="shared" ref="C3:C14" si="0">ROUND(B3*5/155, 2)</f>
+        <v>0.39</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <f t="shared" ref="E3:E14" si="1">D3*5/100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <f>SUM(Sheet2!B4:AF4)</f>
+        <v>116</v>
+      </c>
+      <c r="C4">
+        <f t="shared" si="0"/>
+        <v>3.74</v>
+      </c>
+      <c r="D4">
+        <v>91</v>
+      </c>
+      <c r="E4">
+        <f t="shared" si="1"/>
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <f>SUM(Sheet2!B5:AF5)</f>
+        <v>13</v>
+      </c>
+      <c r="C5">
+        <f t="shared" si="0"/>
+        <v>0.42</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6">
+        <f>SUM(Sheet2!B6:AF6)</f>
+        <v>128</v>
+      </c>
+      <c r="C6">
+        <f t="shared" si="0"/>
+        <v>4.13</v>
+      </c>
+      <c r="D6">
+        <v>100</v>
+      </c>
+      <c r="E6">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <f>SUM(Sheet2!B7:AF7)</f>
+        <v>109</v>
+      </c>
+      <c r="C7">
+        <f t="shared" si="0"/>
+        <v>3.52</v>
+      </c>
+      <c r="D7">
+        <v>100</v>
+      </c>
+      <c r="E7">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <f>SUM(Sheet2!B8:AF8)</f>
+        <v>116</v>
+      </c>
+      <c r="C8">
+        <f t="shared" si="0"/>
+        <v>3.74</v>
+      </c>
+      <c r="D8">
+        <v>100</v>
+      </c>
+      <c r="E8">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9">
+        <f>SUM(Sheet2!B9:AF9)</f>
+        <v>93</v>
+      </c>
+      <c r="C9">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="D9">
+        <v>91</v>
+      </c>
+      <c r="E9">
+        <f t="shared" si="1"/>
+        <v>4.55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10">
+        <f>SUM(Sheet2!B10:AF10)</f>
+        <v>107</v>
+      </c>
+      <c r="C10">
+        <f t="shared" si="0"/>
+        <v>3.45</v>
+      </c>
+      <c r="D10">
+        <v>100</v>
+      </c>
+      <c r="E10">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11">
+        <f>SUM(Sheet2!B11:AF11)</f>
+        <v>21</v>
+      </c>
+      <c r="C11">
+        <f t="shared" si="0"/>
+        <v>0.68</v>
+      </c>
+      <c r="D11">
+        <v>0</v>
+      </c>
+      <c r="E11">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>12</v>
+      </c>
+      <c r="B12">
+        <f>SUM(Sheet2!B12:AF12)</f>
+        <v>107</v>
+      </c>
+      <c r="C12">
+        <f t="shared" si="0"/>
+        <v>3.45</v>
+      </c>
+      <c r="D12">
+        <v>100</v>
+      </c>
+      <c r="E12">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13">
+        <f>SUM(Sheet2!B13:AF13)</f>
+        <v>69</v>
+      </c>
+      <c r="C13">
+        <f t="shared" si="0"/>
+        <v>2.23</v>
+      </c>
+      <c r="D13">
+        <v>100</v>
+      </c>
+      <c r="E13">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>15</v>
+      </c>
+      <c r="B14">
+        <f>SUM(Sheet2!B14:AF14)</f>
+        <v>22</v>
+      </c>
+      <c r="C14">
+        <f t="shared" si="0"/>
+        <v>0.71</v>
+      </c>
+      <c r="D14">
+        <v>0</v>
+      </c>
+      <c r="E14">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A98C6570-F9B3-4151-ADE7-2470FA86FDC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8525CF39-68D7-46D3-A21D-A5084A0D1408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="2" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -639,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AF14"/>
+  <dimension ref="A1:AG14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -654,7 +654,7 @@
     <col min="28" max="31" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -751,8 +751,11 @@
       <c r="AF1" s="1">
         <v>45590</v>
       </c>
+      <c r="AG1" s="1">
+        <v>45595</v>
+      </c>
     </row>
-    <row r="2" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -849,8 +852,11 @@
       <c r="AF2" t="s">
         <v>10</v>
       </c>
+      <c r="AG2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -947,8 +953,11 @@
       <c r="AF3" t="s">
         <v>10</v>
       </c>
+      <c r="AG3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1045,8 +1054,11 @@
       <c r="AF4" t="s">
         <v>10</v>
       </c>
+      <c r="AG4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1143,8 +1155,11 @@
       <c r="AF5" t="s">
         <v>10</v>
       </c>
+      <c r="AG5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1241,8 +1256,11 @@
       <c r="AF6" t="s">
         <v>9</v>
       </c>
+      <c r="AG6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1339,8 +1357,11 @@
       <c r="AF7" t="s">
         <v>10</v>
       </c>
+      <c r="AG7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1437,8 +1458,11 @@
       <c r="AF8" t="s">
         <v>10</v>
       </c>
+      <c r="AG8" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1535,8 +1559,11 @@
       <c r="AF9" t="s">
         <v>10</v>
       </c>
+      <c r="AG9" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1633,8 +1660,11 @@
       <c r="AF10" t="s">
         <v>9</v>
       </c>
+      <c r="AG10" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1731,8 +1761,11 @@
       <c r="AF11" t="s">
         <v>10</v>
       </c>
+      <c r="AG11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1829,8 +1862,11 @@
       <c r="AF12" t="s">
         <v>10</v>
       </c>
+      <c r="AG12" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1928,7 +1964,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2037,7 +2073,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA73659-E93B-42DB-A97C-57B09528EE56}">
-  <dimension ref="A1:AF14"/>
+  <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -3569,264 +3605,6 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13">
-        <f>_xlfn.IFS(Attendance!B13="P", 5, Attendance!B13="O",3,Attendance!B13="A",0, Attendance!B13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="C13">
-        <f>_xlfn.IFS(Attendance!C13="P", 5, Attendance!C13="O",3,Attendance!C13="A",0, Attendance!C13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="D13">
-        <f>_xlfn.IFS(Attendance!D13="P", 5, Attendance!D13="O",3,Attendance!D13="A",0, Attendance!D13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="E13">
-        <f>_xlfn.IFS(Attendance!E13="P", 5, Attendance!E13="O",3,Attendance!E13="A",0, Attendance!E13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F13">
-        <f>_xlfn.IFS(Attendance!F13="P", 5, Attendance!F13="O",3,Attendance!F13="A",0, Attendance!F13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="G13">
-        <f>_xlfn.IFS(Attendance!G13="P", 5, Attendance!G13="O",3,Attendance!G13="A",0, Attendance!G13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="H13">
-        <f>_xlfn.IFS(Attendance!H13="P", 5, Attendance!H13="O",3,Attendance!H13="A",0, Attendance!H13="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="I13">
-        <f>_xlfn.IFS(Attendance!I13="P", 5, Attendance!I13="O",3,Attendance!I13="A",0, Attendance!I13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="J13">
-        <f>_xlfn.IFS(Attendance!J13="P", 5, Attendance!J13="O",3,Attendance!J13="A",0, Attendance!J13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="K13">
-        <f>_xlfn.IFS(Attendance!K13="P", 5, Attendance!K13="O",3,Attendance!K13="A",0, Attendance!K13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="L13">
-        <f>_xlfn.IFS(Attendance!L13="P", 5, Attendance!L13="O",3,Attendance!L13="A",0, Attendance!L13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="M13">
-        <f>_xlfn.IFS(Attendance!M13="P", 5, Attendance!M13="O",3,Attendance!M13="A",0, Attendance!M13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="N13">
-        <f>_xlfn.IFS(Attendance!N13="P", 5, Attendance!N13="O",3,Attendance!N13="A",0, Attendance!N13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="O13">
-        <f>_xlfn.IFS(Attendance!O13="P", 5, Attendance!O13="O",3,Attendance!O13="A",0, Attendance!O13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="P13">
-        <f>_xlfn.IFS(Attendance!P13="P", 5, Attendance!P13="O",3,Attendance!P13="A",0, Attendance!P13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Q13">
-        <f>_xlfn.IFS(Attendance!Q13="P", 5, Attendance!Q13="O",3,Attendance!Q13="A",0, Attendance!Q13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="R13">
-        <f>_xlfn.IFS(Attendance!R13="P", 5, Attendance!R13="O",3,Attendance!R13="A",0, Attendance!R13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="S13">
-        <f>_xlfn.IFS(Attendance!S13="P", 5, Attendance!S13="O",3,Attendance!S13="A",0, Attendance!S13="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="T13">
-        <f>_xlfn.IFS(Attendance!T13="P", 5, Attendance!T13="O",3,Attendance!T13="A",0, Attendance!T13="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="U13">
-        <f>_xlfn.IFS(Attendance!U13="P", 5, Attendance!U13="O",3,Attendance!U13="A",0, Attendance!U13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="V13">
-        <f>_xlfn.IFS(Attendance!V13="P", 5, Attendance!V13="O",3,Attendance!V13="A",0, Attendance!V13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="W13">
-        <f>_xlfn.IFS(Attendance!W13="P", 5, Attendance!W13="O",3,Attendance!W13="A",0, Attendance!W13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="X13">
-        <f>_xlfn.IFS(Attendance!X13="P", 5, Attendance!X13="O",3,Attendance!X13="A",0, Attendance!X13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Y13">
-        <f>_xlfn.IFS(Attendance!Y13="P", 5, Attendance!Y13="O",3,Attendance!Y13="A",0, Attendance!Y13="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="Z13">
-        <f>_xlfn.IFS(Attendance!Z13="P", 5, Attendance!Z13="O",3,Attendance!Z13="A",0, Attendance!Z13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA13">
-        <f>_xlfn.IFS(Attendance!AA13="P", 5, Attendance!AA13="O",3,Attendance!AA13="A",0, Attendance!AA13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AB13">
-        <f>_xlfn.IFS(Attendance!AB13="P", 5, Attendance!AB13="O",3,Attendance!AB13="A",0, Attendance!AB13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC13">
-        <f>_xlfn.IFS(Attendance!AC13="P", 5, Attendance!AC13="O",3,Attendance!AC13="A",0, Attendance!AC13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD13">
-        <f>_xlfn.IFS(Attendance!AD13="P", 5, Attendance!AD13="O",3,Attendance!AD13="A",0, Attendance!AD13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE13">
-        <f>_xlfn.IFS(Attendance!AE13="P", 5, Attendance!AE13="O",3,Attendance!AE13="A",0, Attendance!AE13="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF13">
-        <f>_xlfn.IFS(Attendance!AF13="P", 5, Attendance!AF13="O",3,Attendance!AF13="A",0, Attendance!AF13="N/A",0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <f>_xlfn.IFS(Attendance!B14="P", 5, Attendance!B14="O",3,Attendance!B14="A",0, Attendance!B14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="C14">
-        <f>_xlfn.IFS(Attendance!C14="P", 5, Attendance!C14="O",3,Attendance!C14="A",0, Attendance!C14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="D14">
-        <f>_xlfn.IFS(Attendance!D14="P", 5, Attendance!D14="O",3,Attendance!D14="A",0, Attendance!D14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f>_xlfn.IFS(Attendance!E14="P", 5, Attendance!E14="O",3,Attendance!E14="A",0, Attendance!E14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="F14">
-        <f>_xlfn.IFS(Attendance!F14="P", 5, Attendance!F14="O",3,Attendance!F14="A",0, Attendance!F14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <f>_xlfn.IFS(Attendance!G14="P", 5, Attendance!G14="O",3,Attendance!G14="A",0, Attendance!G14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="H14">
-        <f>_xlfn.IFS(Attendance!H14="P", 5, Attendance!H14="O",3,Attendance!H14="A",0, Attendance!H14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="I14">
-        <f>_xlfn.IFS(Attendance!I14="P", 5, Attendance!I14="O",3,Attendance!I14="A",0, Attendance!I14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="J14">
-        <f>_xlfn.IFS(Attendance!J14="P", 5, Attendance!J14="O",3,Attendance!J14="A",0, Attendance!J14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="K14">
-        <f>_xlfn.IFS(Attendance!K14="P", 5, Attendance!K14="O",3,Attendance!K14="A",0, Attendance!K14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="L14">
-        <f>_xlfn.IFS(Attendance!L14="P", 5, Attendance!L14="O",3,Attendance!L14="A",0, Attendance!L14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="M14">
-        <f>_xlfn.IFS(Attendance!M14="P", 5, Attendance!M14="O",3,Attendance!M14="A",0, Attendance!M14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="N14">
-        <f>_xlfn.IFS(Attendance!N14="P", 5, Attendance!N14="O",3,Attendance!N14="A",0, Attendance!N14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="O14">
-        <f>_xlfn.IFS(Attendance!O14="P", 5, Attendance!O14="O",3,Attendance!O14="A",0, Attendance!O14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="P14">
-        <f>_xlfn.IFS(Attendance!P14="P", 5, Attendance!P14="O",3,Attendance!P14="A",0, Attendance!P14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q14">
-        <f>_xlfn.IFS(Attendance!Q14="P", 5, Attendance!Q14="O",3,Attendance!Q14="A",0, Attendance!Q14="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="R14">
-        <f>_xlfn.IFS(Attendance!R14="P", 5, Attendance!R14="O",3,Attendance!R14="A",0, Attendance!R14="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="S14">
-        <f>_xlfn.IFS(Attendance!S14="P", 5, Attendance!S14="O",3,Attendance!S14="A",0, Attendance!S14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="T14">
-        <f>_xlfn.IFS(Attendance!T14="P", 5, Attendance!T14="O",3,Attendance!T14="A",0, Attendance!T14="N/A",0)</f>
-        <v>5</v>
-      </c>
-      <c r="U14">
-        <f>_xlfn.IFS(Attendance!U14="P", 5, Attendance!U14="O",3,Attendance!U14="A",0, Attendance!U14="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="V14">
-        <f>_xlfn.IFS(Attendance!V14="P", 5, Attendance!V14="O",3,Attendance!V14="A",0, Attendance!V14="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="W14">
-        <f>_xlfn.IFS(Attendance!W14="P", 5, Attendance!W14="O",3,Attendance!W14="A",0, Attendance!W14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="X14">
-        <f>_xlfn.IFS(Attendance!X14="P", 5, Attendance!X14="O",3,Attendance!X14="A",0, Attendance!X14="N/A",0)</f>
-        <v>3</v>
-      </c>
-      <c r="Y14">
-        <f>_xlfn.IFS(Attendance!Y14="P", 5, Attendance!Y14="O",3,Attendance!Y14="A",0, Attendance!Y14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="Z14">
-        <f>_xlfn.IFS(Attendance!Z14="P", 5, Attendance!Z14="O",3,Attendance!Z14="A",0, Attendance!Z14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AA14">
-        <f>_xlfn.IFS(Attendance!AA14="P", 5, Attendance!AA14="O",3,Attendance!AA14="A",0, Attendance!AA14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AB14">
-        <f>_xlfn.IFS(Attendance!AB14="P", 5, Attendance!AB14="O",3,Attendance!AB14="A",0, Attendance!AB14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AC14">
-        <f>_xlfn.IFS(Attendance!AC14="P", 5, Attendance!AC14="O",3,Attendance!AC14="A",0, Attendance!AC14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AD14">
-        <f>_xlfn.IFS(Attendance!AD14="P", 5, Attendance!AD14="O",3,Attendance!AD14="A",0, Attendance!AD14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AE14">
-        <f>_xlfn.IFS(Attendance!AE14="P", 5, Attendance!AE14="O",3,Attendance!AE14="A",0, Attendance!AE14="N/A",0)</f>
-        <v>0</v>
-      </c>
-      <c r="AF14">
-        <f>_xlfn.IFS(Attendance!AF14="P", 5, Attendance!AF14="O",3,Attendance!AF14="A",0, Attendance!AF14="N/A",0)</f>
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -3835,7 +3613,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B78BAD9-C027-4A50-86F1-B5BC62C95462}">
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -3891,14 +3669,14 @@
         <v>12</v>
       </c>
       <c r="C3">
-        <f t="shared" ref="C3:C14" si="0">ROUND(B3*5/155, 2)</f>
+        <f t="shared" ref="C3:C12" si="0">ROUND(B3*5/155, 2)</f>
         <v>0.39</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <f t="shared" ref="E3:E14" si="1">D3*5/100</f>
+        <f t="shared" ref="E3:E12" si="1">D3*5/100</f>
         <v>0</v>
       </c>
     </row>
@@ -4080,46 +3858,6 @@
       <c r="E12">
         <f t="shared" si="1"/>
         <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13">
-        <f>SUM(Sheet2!B13:AF13)</f>
-        <v>69</v>
-      </c>
-      <c r="C13">
-        <f t="shared" si="0"/>
-        <v>2.23</v>
-      </c>
-      <c r="D13">
-        <v>100</v>
-      </c>
-      <c r="E13">
-        <f t="shared" si="1"/>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" t="s">
-        <v>15</v>
-      </c>
-      <c r="B14">
-        <f>SUM(Sheet2!B14:AF14)</f>
-        <v>22</v>
-      </c>
-      <c r="C14">
-        <f t="shared" si="0"/>
-        <v>0.71</v>
-      </c>
-      <c r="D14">
-        <v>0</v>
-      </c>
-      <c r="E14">
-        <f t="shared" si="1"/>
-        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8525CF39-68D7-46D3-A21D-A5084A0D1408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DC45C7-7F60-456D-9352-A5A7038E3804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="456" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -639,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AG14"/>
+  <dimension ref="A1:AK14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -654,7 +654,7 @@
     <col min="28" max="31" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -754,8 +754,20 @@
       <c r="AG1" s="1">
         <v>45595</v>
       </c>
+      <c r="AH1" s="1">
+        <v>45601</v>
+      </c>
+      <c r="AI1" s="1">
+        <v>45604</v>
+      </c>
+      <c r="AJ1" s="1">
+        <v>45608</v>
+      </c>
+      <c r="AK1" s="1">
+        <v>45611</v>
+      </c>
     </row>
-    <row r="2" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -855,8 +867,20 @@
       <c r="AG2" t="s">
         <v>10</v>
       </c>
+      <c r="AH2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -956,8 +980,20 @@
       <c r="AG3" t="s">
         <v>10</v>
       </c>
+      <c r="AH3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1057,8 +1093,20 @@
       <c r="AG4" t="s">
         <v>10</v>
       </c>
+      <c r="AH4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK4" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1158,8 +1206,20 @@
       <c r="AG5" t="s">
         <v>9</v>
       </c>
+      <c r="AH5" t="s">
+        <v>11</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK5" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1259,8 +1319,20 @@
       <c r="AG6" t="s">
         <v>9</v>
       </c>
+      <c r="AH6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1360,8 +1432,20 @@
       <c r="AG7" t="s">
         <v>10</v>
       </c>
+      <c r="AH7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1461,8 +1545,20 @@
       <c r="AG8" t="s">
         <v>10</v>
       </c>
+      <c r="AH8" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK8" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1562,8 +1658,20 @@
       <c r="AG9" t="s">
         <v>9</v>
       </c>
+      <c r="AH9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI9" t="s">
+        <v>11</v>
+      </c>
+      <c r="AJ9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK9" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1663,8 +1771,20 @@
       <c r="AG10" t="s">
         <v>9</v>
       </c>
+      <c r="AH10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AI10" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AK10" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1764,8 +1884,20 @@
       <c r="AG11" t="s">
         <v>10</v>
       </c>
+      <c r="AH11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -1865,8 +1997,20 @@
       <c r="AG12" t="s">
         <v>10</v>
       </c>
+      <c r="AH12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -1963,8 +2107,23 @@
       <c r="AF13" t="s">
         <v>13</v>
       </c>
+      <c r="AG13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK13" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2059,6 +2218,21 @@
         <v>13</v>
       </c>
       <c r="AF14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AG14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AH14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AI14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AJ14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AK14" t="s">
         <v>13</v>
       </c>
     </row>

--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8DC45C7-7F60-456D-9352-A5A7038E3804}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B41CC63-54B6-4EE9-B2B0-B03AF7E771DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -639,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AK14"/>
+  <dimension ref="A1:AM14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -654,7 +654,7 @@
     <col min="28" max="31" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -766,8 +766,14 @@
       <c r="AK1" s="1">
         <v>45611</v>
       </c>
+      <c r="AL1" s="1">
+        <v>45616</v>
+      </c>
+      <c r="AM1" s="1">
+        <v>45623</v>
+      </c>
     </row>
-    <row r="2" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -879,8 +885,14 @@
       <c r="AK2" t="s">
         <v>10</v>
       </c>
+      <c r="AL2" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -992,8 +1004,14 @@
       <c r="AK3" t="s">
         <v>10</v>
       </c>
+      <c r="AL3" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1105,8 +1123,14 @@
       <c r="AK4" t="s">
         <v>10</v>
       </c>
+      <c r="AL4" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1218,8 +1242,14 @@
       <c r="AK5" t="s">
         <v>10</v>
       </c>
+      <c r="AL5" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1331,8 +1361,14 @@
       <c r="AK6" t="s">
         <v>9</v>
       </c>
+      <c r="AL6" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1444,8 +1480,14 @@
       <c r="AK7" t="s">
         <v>10</v>
       </c>
+      <c r="AL7" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1557,8 +1599,14 @@
       <c r="AK8" t="s">
         <v>9</v>
       </c>
+      <c r="AL8" t="s">
+        <v>11</v>
+      </c>
+      <c r="AM8" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1670,8 +1718,14 @@
       <c r="AK9" t="s">
         <v>10</v>
       </c>
+      <c r="AL9" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM9" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1783,8 +1837,14 @@
       <c r="AK10" t="s">
         <v>10</v>
       </c>
+      <c r="AL10" t="s">
+        <v>9</v>
+      </c>
+      <c r="AM10" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1896,8 +1956,14 @@
       <c r="AK11" t="s">
         <v>10</v>
       </c>
+      <c r="AL11" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2009,8 +2075,14 @@
       <c r="AK12" t="s">
         <v>10</v>
       </c>
+      <c r="AL12" t="s">
+        <v>10</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -2122,8 +2194,14 @@
       <c r="AK13" t="s">
         <v>13</v>
       </c>
+      <c r="AL13" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM13" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2233,6 +2311,12 @@
         <v>13</v>
       </c>
       <c r="AK14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AL14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AM14" t="s">
         <v>13</v>
       </c>
     </row>

--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B41CC63-54B6-4EE9-B2B0-B03AF7E771DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B772A9C-05F3-4ABF-815F-9136096394E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
     <sheet name="Attendance" sheetId="2" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="22">
   <si>
     <t>Name</t>
   </si>
@@ -639,7 +639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
-  <dimension ref="A1:AM14"/>
+  <dimension ref="A1:AN14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
@@ -654,7 +654,7 @@
     <col min="28" max="31" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -772,8 +772,11 @@
       <c r="AM1" s="1">
         <v>45623</v>
       </c>
+      <c r="AN1" s="1">
+        <v>45625</v>
+      </c>
     </row>
-    <row r="2" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
@@ -891,8 +894,11 @@
       <c r="AM2" t="s">
         <v>10</v>
       </c>
+      <c r="AN2" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="3" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>17</v>
       </c>
@@ -1010,8 +1016,11 @@
       <c r="AM3" t="s">
         <v>10</v>
       </c>
+      <c r="AN3" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="4" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1</v>
       </c>
@@ -1129,8 +1138,11 @@
       <c r="AM4" t="s">
         <v>9</v>
       </c>
+      <c r="AN4" t="s">
+        <v>11</v>
+      </c>
     </row>
-    <row r="5" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>16</v>
       </c>
@@ -1248,8 +1260,11 @@
       <c r="AM5" t="s">
         <v>9</v>
       </c>
+      <c r="AN5" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="6" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>8</v>
       </c>
@@ -1367,8 +1382,11 @@
       <c r="AM6" t="s">
         <v>9</v>
       </c>
+      <c r="AN6" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="7" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>2</v>
       </c>
@@ -1486,8 +1504,11 @@
       <c r="AM7" t="s">
         <v>10</v>
       </c>
+      <c r="AN7" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="8" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>4</v>
       </c>
@@ -1605,8 +1626,11 @@
       <c r="AM8" t="s">
         <v>9</v>
       </c>
+      <c r="AN8" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="9" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>6</v>
       </c>
@@ -1724,8 +1748,11 @@
       <c r="AM9" t="s">
         <v>10</v>
       </c>
+      <c r="AN9" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="10" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>7</v>
       </c>
@@ -1843,8 +1870,11 @@
       <c r="AM10" t="s">
         <v>9</v>
       </c>
+      <c r="AN10" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="11" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -1962,8 +1992,11 @@
       <c r="AM11" t="s">
         <v>10</v>
       </c>
+      <c r="AN11" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="12" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>12</v>
       </c>
@@ -2081,8 +2114,11 @@
       <c r="AM12" t="s">
         <v>10</v>
       </c>
+      <c r="AN12" t="s">
+        <v>10</v>
+      </c>
     </row>
-    <row r="13" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>5</v>
       </c>
@@ -2200,8 +2236,11 @@
       <c r="AM13" t="s">
         <v>13</v>
       </c>
+      <c r="AN13" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="14" spans="1:39" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:40" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -2317,6 +2356,9 @@
         <v>13</v>
       </c>
       <c r="AM14" t="s">
+        <v>13</v>
+      </c>
+      <c r="AN14" t="s">
         <v>13</v>
       </c>
     </row>

--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -1,21 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B772A9C-05F3-4ABF-815F-9136096394E1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF0C09A-9178-485B-AEFE-975E6918A250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
   <sheets>
-    <sheet name="Attendance" sheetId="2" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
+    <sheet name="Attendance2025" sheetId="5" r:id="rId1"/>
+    <sheet name="Attendance" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="549" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -94,6 +95,21 @@
   <si>
     <t>Test Performance/5</t>
   </si>
+  <si>
+    <t>Dev</t>
+  </si>
+  <si>
+    <t>Nilay</t>
+  </si>
+  <si>
+    <t>Dhruvi</t>
+  </si>
+  <si>
+    <t>Tithi</t>
+  </si>
+  <si>
+    <t>Het</t>
+  </si>
 </sst>
 </file>
 
@@ -128,9 +144,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -638,20 +655,68 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B591F8-E2D2-49D1-AD57-B281540FCEF2}">
+  <dimension ref="A1:F2"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2">
+        <v>45653</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{126A5D5F-C148-4702-AC91-410419350378}">
   <dimension ref="A1:AN14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="25" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
-    <col min="28" max="31" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="28" max="33" width="6.5546875" bestFit="1" customWidth="1"/>
+    <col min="34" max="40" width="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:40" x14ac:dyDescent="0.3">
@@ -2371,19 +2436,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAA73659-E93B-42DB-A97C-57B09528EE56}">
   <dimension ref="A1:AF12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="4" width="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="5.44140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="6.44140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="6.21875" bestFit="1" customWidth="1"/>
-    <col min="13" max="16" width="7.21875" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="5.33203125" bestFit="1" customWidth="1"/>
-    <col min="19" max="25" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="10" width="6.44140625" bestFit="1" customWidth="1"/>
+    <col min="11" max="16" width="7.21875" bestFit="1" customWidth="1"/>
+    <col min="17" max="25" width="6.33203125" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="6.6640625" bestFit="1" customWidth="1"/>
     <col min="28" max="32" width="6.5546875" bestFit="1" customWidth="1"/>
   </cols>
@@ -3911,7 +3973,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B78BAD9-C027-4A50-86F1-B5BC62C95462}">
   <dimension ref="A1:E12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>

--- a/22club2_LJ_4PM/DS/Attendance.xlsx
+++ b/22club2_LJ_4PM/DS/Attendance.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alakh Pandya\Desktop\all_batches\22club2_LJ_4PM\DS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF0C09A-9178-485B-AEFE-975E6918A250}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BA8AE5-42DD-474A-84B5-B6F8CFE4B6C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{822180F9-E4E2-4D10-B8F7-229F5B87376E}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="559" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="27">
   <si>
     <t>Name</t>
   </si>
@@ -656,7 +656,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E2B591F8-E2D2-49D1-AD57-B281540FCEF2}">
-  <dimension ref="A1:F2"/>
+  <dimension ref="A1:F3"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
@@ -697,6 +697,26 @@
       </c>
       <c r="F2" t="s">
         <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2">
+        <v>45658</v>
+      </c>
+      <c r="B3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
